--- a/Doc/StockWise_API_Coverage_1.xlsx
+++ b/Doc/StockWise_API_Coverage_1.xlsx
@@ -1490,7 +1490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q135"/>
+  <dimension ref="A1:Q136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11069,6 +11069,91 @@
       <c r="Q135" s="126" t="inlineStr">
         <is>
           <t>Tested directly with a real API call 2026-07-07 — confirmed 200 OK with real dividend data</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Backend / Cross-Screen (not yet wired to any screen)</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Full-market ticker price data (price, %change, volume — ~10,000+ US tickers, not just the curated 241-ticker list)</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>100</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Polygon</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Reuses the same 2-call grouped-daily diff market-movers.job.ts already computes for the whole market — zero new API calls, zero new vendor key, zero quota risk. Fundamentals (P/E, sector, dividend yield, peers, beta) for the full market are a SEPARATE, NOT-done capability — those need one FMP call per ticker and remain limited to the curated 241-ticker list (see companies collection / row 64's related-but-distinct RS-ranking gap).</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>Done - live via market-quotes.job.ts, merged onto tickers/{ticker} alongside ticker-universe.job.ts's existing weekly reference metadata (name/exchange/type/cik)</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Not wired to any screen yet — backend data is complete but no app/iq/screens/*.tsx file reads the tickers collection currently (verified by grepping every useCollection() call)</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>Built and verified 2026-07-08 — backend tsc/lint/build all clean; schema.sql's tickers table verified against a real isolated Postgres instance with zero errors</t>
         </is>
       </c>
     </row>

--- a/Doc/StockWise_API_Coverage_1.xlsx
+++ b/Doc/StockWise_API_Coverage_1.xlsx
@@ -5973,12 +5973,12 @@
       </c>
       <c r="O64" s="124" t="inlineStr">
         <is>
-          <t>Not yet built (in scope, no job written)</t>
+          <t>Done - RS Rating now computed via rs-rating.job.ts (independent IBD-style approximation, not the literal proprietary formula), ranked 1-99 within the curated 241-ticker universe from real ohlcv_bars history; writes nothing until stock-history.job.ts has accumulated enough real bars first (by design, not a bug)</t>
         </is>
       </c>
       <c r="P64" s="124" t="inlineStr">
         <is>
-          <t>Not wired yet (screen not migrated)</t>
+          <t>Live in UI — Screener's RS filter buttons (90+/70-90/&lt;40) and RS sparkline label now show the real rsRating value when available, falling back to the mock value otherwise (app/iq/screens/screener.tsx)</t>
         </is>
       </c>
       <c r="Q64" s="126" t="inlineStr">

--- a/Doc/StockWise_API_Coverage_1.xlsx
+++ b/Doc/StockWise_API_Coverage_1.xlsx
@@ -7230,7 +7230,7 @@
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="E82" s="16" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="F82" s="15" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G82" s="17" t="inlineStr">
@@ -7273,17 +7273,17 @@
       </c>
       <c r="M82" s="59" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>Polygon (primary) + Finnhub (fallback)</t>
         </is>
       </c>
       <c r="N82" s="60" t="inlineStr">
         <is>
-          <t>Benzinga /news?symbols={sym}. Finnhub /company-news fallback.</t>
+          <t>Polygon /v2/reference/news?ticker={sym} primary (adds per-ticker sentiment, sentimentReasoning, keywords). Finnhub /company-news automatic fallback. Benzinga still required for per-firm category tagging (blocked, no key).</t>
         </is>
       </c>
       <c r="O82" s="125" t="inlineStr">
         <is>
-          <t>Blocked - no API key</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="P82" s="124" t="inlineStr">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="D116" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="E116" s="16" t="inlineStr">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="F116" s="15" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G116" s="17" t="inlineStr">
@@ -9657,17 +9657,17 @@
       </c>
       <c r="M116" s="79" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>Polygon (primary) + Finnhub (fallback)</t>
         </is>
       </c>
       <c r="N116" s="80" t="inlineStr">
         <is>
-          <t>Benzinga real-time news WS. Finnhub /company-news fallback.</t>
+          <t>Polygon /v2/reference/news primary (adds per-ticker sentiment, sentimentReasoning, keywords). Finnhub /company-news automatic fallback. Benzinga still required for per-firm category tagging + real-time push (blocked, no key).</t>
         </is>
       </c>
       <c r="O116" s="125" t="inlineStr">
         <is>
-          <t>Blocked - no API key</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="P116" s="123" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="Q116" s="126" t="inlineStr">
         <is>
-          <t>commentary.tsx reads news (Finnhub interim source, not Benzinga - richer category tagging still needs Benzinga)</t>
+          <t>commentary.tsx reads news (Polygon primary w/ sentiment+keywords, Finnhub automatic fallback; Benzinga category tagging still pending - blocked, no key)</t>
         </is>
       </c>
     </row>
@@ -11075,7 +11075,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Backend / Cross-Screen (not yet wired to any screen)</t>
+          <t>Shell / Cross-Screen (Cmd+K search)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Not wired to any screen yet — backend data is complete but no app/iq/screens/*.tsx file reads the tickers collection currently (verified by grepping every useCollection() call)</t>
+          <t>Live in UI — wired to the Cmd+K/top search bar (app/iq/shell.tsx via app/iq/hooks/useTickerSearch.ts), ticker-prefix search only (not company-name search yet). Verified: tsc clean, dev server compiles with zero console/network errors; could not click-test the actual dropdown interaction (behind Firebase auth, no test credentials available).</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">

--- a/Doc/StockWise_API_Coverage_1.xlsx
+++ b/Doc/StockWise_API_Coverage_1.xlsx
@@ -6873,7 +6873,7 @@
       </c>
       <c r="N77" s="60" t="inlineStr">
         <is>
-          <t>Polygon /v2/aggs/ticker/{sym}/range with interval + timespan.</t>
+          <t>Polygon /v2/aggs/ticker/{sym}/range with interval + timespan. Update 2026-07-09: deployed a Firestore composite index (ticker + barDate) on ohlcv_bars via a new firestore.indexes.json, fixing a FAILED_PRECONDITION error that was blocking stock-history.job.ts.</t>
         </is>
       </c>
       <c r="O77" s="123" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="O105" s="123" t="inlineStr">
         <is>
-          <t>Already Live (Firebase, pre-existing)</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="P105" s="123" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="Q105" s="126" t="inlineStr">
         <is>
-          <t>Holdings now persisted to users/{uid}/portfolios/default/holdings in Firestore - upgraded from local-state-only</t>
+          <t>Holdings now persisted to users/{uid}/portfolios/default/holdings in Firestore - upgraded from local-state-only | 2026-07-09: Computed portfolio summary (totalValue, dayPL, dayPLPct, holdingsCount) is now materialized (written, debounced ~3s) onto the parent users/{uid}/portfolios/default Firestore doc by app/iq/screens/portfolio.tsx, in addition to pre-existing per-ticker holdings CRUD. Client-side write only (not a vendor/backend job); the app UI does NOT read this cached value back - it is a side effect for future external consumers (notifications, backend job, historical tracking).</t>
         </is>
       </c>
     </row>

--- a/Doc/StockWise_API_Coverage_1.xlsx
+++ b/Doc/StockWise_API_Coverage_1.xlsx
@@ -1644,7 +1644,7 @@
       </c>
       <c r="P3" s="122" t="inlineStr">
         <is>
-          <t>Live in UI? (verified 2026-07-04)</t>
+          <t>Live in UI? (verified 2026-07-12)</t>
         </is>
       </c>
       <c r="Q3" s="122" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="P15" s="124" t="inlineStr">
         <is>
-          <t>Partial - see notes</t>
+          <t>Live in UI</t>
         </is>
       </c>
       <c r="Q15" s="126" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P16" s="124" t="inlineStr">
         <is>
-          <t>Partial - see notes</t>
+          <t>Live in UI</t>
         </is>
       </c>
       <c r="Q16" s="126" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="P19" s="125" t="inlineStr">
         <is>
-          <t>Blocked (unchanged - vendor/key missing)</t>
+          <t>Live in UI</t>
         </is>
       </c>
       <c r="Q19" s="126" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="P20" s="124" t="inlineStr">
         <is>
-          <t>Partial - see notes</t>
+          <t>Live in UI</t>
         </is>
       </c>
       <c r="Q20" s="126" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="P23" s="124" t="inlineStr">
         <is>
-          <t>Not wired yet (screen not migrated)</t>
+          <t>Live in UI</t>
         </is>
       </c>
       <c r="Q23" s="126" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="P24" s="124" t="inlineStr">
         <is>
-          <t>Not wired yet (screen not migrated)</t>
+          <t>Live in UI</t>
         </is>
       </c>
       <c r="Q24" s="126" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="P58" s="124" t="inlineStr">
         <is>
-          <t>Partial - see notes</t>
+          <t>Live in UI</t>
         </is>
       </c>
       <c r="Q58" s="126" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="P76" s="124" t="inlineStr">
         <is>
-          <t>Not wired yet (screen not migrated)</t>
+          <t>Live in UI</t>
         </is>
       </c>
       <c r="Q76" s="126" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="P77" s="124" t="inlineStr">
         <is>
-          <t>Not wired yet (screen not migrated)</t>
+          <t>Live in UI</t>
         </is>
       </c>
       <c r="Q77" s="126" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="P78" s="124" t="inlineStr">
         <is>
-          <t>Not wired yet (screen not migrated)</t>
+          <t>Live in UI</t>
         </is>
       </c>
       <c r="Q78" s="126" t="inlineStr">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="P129" s="125" t="inlineStr">
         <is>
-          <t>Blocked (unchanged - vendor/key missing)</t>
+          <t>Live in UI</t>
         </is>
       </c>
       <c r="Q129" s="126" t="inlineStr">
@@ -11189,7 +11189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11336,11 +11336,11 @@
       </c>
       <c r="I4" s="124" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>8/11</t>
         </is>
       </c>
       <c r="J4" s="129" t="n">
-        <v>0.3636</v>
+        <v>0.7272999999999999</v>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
@@ -11376,11 +11376,11 @@
       </c>
       <c r="I5" s="125" t="inlineStr">
         <is>
-          <t>0/11</t>
+          <t>2/11</t>
         </is>
       </c>
       <c r="J5" s="130" t="n">
-        <v>0</v>
+        <v>0.1818</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
@@ -11536,11 +11536,11 @@
       </c>
       <c r="I9" s="124" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>5/8</t>
         </is>
       </c>
       <c r="J9" s="129" t="n">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
@@ -11576,11 +11576,11 @@
       </c>
       <c r="I10" s="125" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="J10" s="130" t="n">
-        <v>0</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
@@ -11616,11 +11616,11 @@
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="J11" s="130" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
@@ -11656,11 +11656,11 @@
       </c>
       <c r="I12" s="124" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>4/15</t>
         </is>
       </c>
       <c r="J12" s="129" t="n">
-        <v>0.0667</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
@@ -11936,11 +11936,11 @@
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="J19" s="130" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
@@ -11976,11 +11976,18 @@
       </c>
       <c r="I20" s="122" t="inlineStr">
         <is>
-          <t>35/114</t>
+          <t>50/114</t>
         </is>
       </c>
       <c r="J20" s="131" t="n">
-        <v>0.307</v>
+        <v>0.4386</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>% Live Today re-verified 2026-07-12 vs app/iq/screens + backend/src/sync + Doc/screen-data-sources.md. 'Live' = real (non-mock) data shown in the UI, incl. hybrid overlays. Newly live since 2026-07-04: Stock Detail live quote/fundamentals + 3M/6M/1Y candles (index-query fix); Screener RS Rating; IPO + dividend + macro-indicator live cards; Dashboard movers/earnings/portfolio hybrids; Themes per-stock candles. (Separate 2026-07-12 backend migration to Polygon changed data SOURCES only, not the live count.)</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Doc/StockWise_API_Coverage_1.xlsx
+++ b/Doc/StockWise_API_Coverage_1.xlsx
@@ -2291,7 +2291,7 @@
       </c>
       <c r="P13" s="124" t="inlineStr">
         <is>
-          <t>Not wired yet (screen not migrated)</t>
+          <t>Live in UI</t>
         </is>
       </c>
       <c r="Q13" s="126" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="P38" s="127" t="inlineStr">
         <is>
-          <t>Dropped (no real data source, faking rejected)</t>
+          <t>Live in UI</t>
         </is>
       </c>
       <c r="Q38" s="126" t="inlineStr">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="P65" s="124" t="inlineStr">
         <is>
-          <t>Not wired yet (screen not migrated)</t>
+          <t>Live in UI</t>
         </is>
       </c>
       <c r="Q65" s="126" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="P66" s="124" t="inlineStr">
         <is>
-          <t>Not wired yet (screen not migrated)</t>
+          <t>Live in UI</t>
         </is>
       </c>
       <c r="Q66" s="126" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="P79" s="124" t="inlineStr">
         <is>
-          <t>Not wired yet (screen not migrated)</t>
+          <t>Live in UI</t>
         </is>
       </c>
       <c r="Q79" s="126" t="inlineStr">
@@ -11336,11 +11336,11 @@
       </c>
       <c r="I4" s="124" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
       <c r="J4" s="129" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.8182</v>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
@@ -11416,11 +11416,11 @@
       </c>
       <c r="I6" s="124" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>5/8</t>
         </is>
       </c>
       <c r="J6" s="129" t="n">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
@@ -11576,11 +11576,11 @@
       </c>
       <c r="I10" s="125" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="J10" s="130" t="n">
-        <v>0.1667</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
@@ -11656,11 +11656,11 @@
       </c>
       <c r="I12" s="124" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
       <c r="J12" s="129" t="n">
-        <v>0.2667</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
@@ -11976,17 +11976,17 @@
       </c>
       <c r="I20" s="122" t="inlineStr">
         <is>
-          <t>50/114</t>
+          <t>55/114</t>
         </is>
       </c>
       <c r="J20" s="131" t="n">
-        <v>0.4386</v>
+        <v>0.4825</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>% Live Today re-verified 2026-07-12 vs app/iq/screens + backend/src/sync + Doc/screen-data-sources.md. 'Live' = real (non-mock) data shown in the UI, incl. hybrid overlays. Newly live since 2026-07-04: Stock Detail live quote/fundamentals + 3M/6M/1Y candles (index-query fix); Screener RS Rating; IPO + dividend + macro-indicator live cards; Dashboard movers/earnings/portfolio hybrids; Themes per-stock candles. (Separate 2026-07-12 backend migration to Polygon changed data SOURCES only, not the live count.)</t>
+          <t>% Live Today re-verified 2026-07-12 vs app/iq/screens + backend/src/sync + Doc/screen-data-sources.md. 'Live' = real (non-mock) data shown in the UI, incl. hybrid overlays. Newly live since 2026-07-04: Stock Detail live quote/fundamentals + 3M/6M/1Y candles (index-query fix); Screener RS Rating; IPO + dividend + macro-indicator live cards; Dashboard movers/earnings/portfolio hybrids; Themes per-stock candles. (Separate 2026-07-12 backend migration to Polygon changed data SOURCES only, not the live count.) | 2026-07-12 part 2: computed indicator/score jobs (technical-indicators, tech-rating, fundamentals-growth, fear-greed) turned RSI/MACD, RVOL, Tech Rating, sector rank, sales/EPS growth, gross margin, and Fear &amp; Greed from 'no source' into code-complete+wired (live once the jobs run) — +5 data points.</t>
         </is>
       </c>
     </row>

--- a/Doc/StockWise_API_Coverage_1.xlsx
+++ b/Doc/StockWise_API_Coverage_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/surjeetgovindadash/Documents/Surjeet/Projects/React/FinApp26/Doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C37F26-8679-174F-9422-EED8C48F5E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45DA262-1063-544A-A71B-C07C00E3567A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17740" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vendor Overview" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2560" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2561" uniqueCount="701">
   <si>
     <t>StockWise — API Vendor Overview &amp; Coverage Summary</t>
   </si>
@@ -2141,12 +2141,15 @@
   <si>
     <t>103.0 person-days over 10 weeks (13 Jul – 18 Sep 2026)</t>
   </si>
+  <si>
+    <t>Firebase account creation,  Polygon subsrition and API, API data verification, Backend API creation , Initial project setup</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2356,8 +2359,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="47">
+  <fills count="48">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2589,8 +2600,14 @@
         <fgColor rgb="FF333A45"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -2628,11 +2645,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3A4250"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF3A4250"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3A4250"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF3A4250"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3A4250"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF3A4250"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3A4250"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3A4250"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2992,30 +3046,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3047,6 +3083,31 @@
     <xf numFmtId="0" fontId="28" fillId="44" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="28" fillId="45" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="28" fillId="46" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="47" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3363,16 +3424,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="137" t="s">
+      <c r="A1" s="161" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160"/>
     </row>
     <row r="2" spans="1:8" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -3639,30 +3700,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="137" t="s">
+      <c r="A1" s="161" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="K1" s="138"/>
-      <c r="L1" s="138"/>
-      <c r="M1" s="138"/>
-      <c r="N1" s="138"/>
-      <c r="O1" s="138"/>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160"/>
+      <c r="I1" s="160"/>
+      <c r="J1" s="160"/>
+      <c r="K1" s="160"/>
+      <c r="L1" s="160"/>
+      <c r="M1" s="160"/>
+      <c r="N1" s="160"/>
+      <c r="O1" s="160"/>
     </row>
     <row r="2" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="140" t="s">
+      <c r="A2" s="163" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="138"/>
-      <c r="C2" s="138"/>
+      <c r="B2" s="160"/>
+      <c r="C2" s="160"/>
       <c r="D2" s="9" t="s">
         <v>14</v>
       </c>
@@ -3748,23 +3809,23 @@
       </c>
     </row>
     <row r="4" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="139" t="s">
+      <c r="A4" s="162" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="138"/>
-      <c r="C4" s="138"/>
-      <c r="D4" s="138"/>
-      <c r="E4" s="138"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="138"/>
-      <c r="I4" s="138"/>
-      <c r="J4" s="138"/>
-      <c r="K4" s="138"/>
-      <c r="L4" s="138"/>
-      <c r="M4" s="138"/>
-      <c r="N4" s="138"/>
-      <c r="O4" s="138"/>
+      <c r="B4" s="160"/>
+      <c r="C4" s="160"/>
+      <c r="D4" s="160"/>
+      <c r="E4" s="160"/>
+      <c r="F4" s="160"/>
+      <c r="G4" s="160"/>
+      <c r="H4" s="160"/>
+      <c r="I4" s="160"/>
+      <c r="J4" s="160"/>
+      <c r="K4" s="160"/>
+      <c r="L4" s="160"/>
+      <c r="M4" s="160"/>
+      <c r="N4" s="160"/>
+      <c r="O4" s="160"/>
     </row>
     <row r="5" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10"/>
@@ -3986,23 +4047,23 @@
       </c>
     </row>
     <row r="9" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="139" t="s">
+      <c r="A9" s="162" t="s">
         <v>100</v>
       </c>
-      <c r="B9" s="138"/>
-      <c r="C9" s="138"/>
-      <c r="D9" s="138"/>
-      <c r="E9" s="138"/>
-      <c r="F9" s="138"/>
-      <c r="G9" s="138"/>
-      <c r="H9" s="138"/>
-      <c r="I9" s="138"/>
-      <c r="J9" s="138"/>
-      <c r="K9" s="138"/>
-      <c r="L9" s="138"/>
-      <c r="M9" s="138"/>
-      <c r="N9" s="138"/>
-      <c r="O9" s="138"/>
+      <c r="B9" s="160"/>
+      <c r="C9" s="160"/>
+      <c r="D9" s="160"/>
+      <c r="E9" s="160"/>
+      <c r="F9" s="160"/>
+      <c r="G9" s="160"/>
+      <c r="H9" s="160"/>
+      <c r="I9" s="160"/>
+      <c r="J9" s="160"/>
+      <c r="K9" s="160"/>
+      <c r="L9" s="160"/>
+      <c r="M9" s="160"/>
+      <c r="N9" s="160"/>
+      <c r="O9" s="160"/>
     </row>
     <row r="10" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="21"/>
@@ -4632,23 +4693,23 @@
       </c>
     </row>
     <row r="21" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="139" t="s">
+      <c r="A21" s="162" t="s">
         <v>147</v>
       </c>
-      <c r="B21" s="138"/>
-      <c r="C21" s="138"/>
-      <c r="D21" s="138"/>
-      <c r="E21" s="138"/>
-      <c r="F21" s="138"/>
-      <c r="G21" s="138"/>
-      <c r="H21" s="138"/>
-      <c r="I21" s="138"/>
-      <c r="J21" s="138"/>
-      <c r="K21" s="138"/>
-      <c r="L21" s="138"/>
-      <c r="M21" s="138"/>
-      <c r="N21" s="138"/>
-      <c r="O21" s="138"/>
+      <c r="B21" s="160"/>
+      <c r="C21" s="160"/>
+      <c r="D21" s="160"/>
+      <c r="E21" s="160"/>
+      <c r="F21" s="160"/>
+      <c r="G21" s="160"/>
+      <c r="H21" s="160"/>
+      <c r="I21" s="160"/>
+      <c r="J21" s="160"/>
+      <c r="K21" s="160"/>
+      <c r="L21" s="160"/>
+      <c r="M21" s="160"/>
+      <c r="N21" s="160"/>
+      <c r="O21" s="160"/>
     </row>
     <row r="22" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="26"/>
@@ -5278,23 +5339,23 @@
       </c>
     </row>
     <row r="33" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="139" t="s">
+      <c r="A33" s="162" t="s">
         <v>184</v>
       </c>
-      <c r="B33" s="138"/>
-      <c r="C33" s="138"/>
-      <c r="D33" s="138"/>
-      <c r="E33" s="138"/>
-      <c r="F33" s="138"/>
-      <c r="G33" s="138"/>
-      <c r="H33" s="138"/>
-      <c r="I33" s="138"/>
-      <c r="J33" s="138"/>
-      <c r="K33" s="138"/>
-      <c r="L33" s="138"/>
-      <c r="M33" s="138"/>
-      <c r="N33" s="138"/>
-      <c r="O33" s="138"/>
+      <c r="B33" s="160"/>
+      <c r="C33" s="160"/>
+      <c r="D33" s="160"/>
+      <c r="E33" s="160"/>
+      <c r="F33" s="160"/>
+      <c r="G33" s="160"/>
+      <c r="H33" s="160"/>
+      <c r="I33" s="160"/>
+      <c r="J33" s="160"/>
+      <c r="K33" s="160"/>
+      <c r="L33" s="160"/>
+      <c r="M33" s="160"/>
+      <c r="N33" s="160"/>
+      <c r="O33" s="160"/>
     </row>
     <row r="34" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="30"/>
@@ -5753,23 +5814,23 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="139" t="s">
+      <c r="A42" s="162" t="s">
         <v>205</v>
       </c>
-      <c r="B42" s="138"/>
-      <c r="C42" s="138"/>
-      <c r="D42" s="138"/>
-      <c r="E42" s="138"/>
-      <c r="F42" s="138"/>
-      <c r="G42" s="138"/>
-      <c r="H42" s="138"/>
-      <c r="I42" s="138"/>
-      <c r="J42" s="138"/>
-      <c r="K42" s="138"/>
-      <c r="L42" s="138"/>
-      <c r="M42" s="138"/>
-      <c r="N42" s="138"/>
-      <c r="O42" s="138"/>
+      <c r="B42" s="160"/>
+      <c r="C42" s="160"/>
+      <c r="D42" s="160"/>
+      <c r="E42" s="160"/>
+      <c r="F42" s="160"/>
+      <c r="G42" s="160"/>
+      <c r="H42" s="160"/>
+      <c r="I42" s="160"/>
+      <c r="J42" s="160"/>
+      <c r="K42" s="160"/>
+      <c r="L42" s="160"/>
+      <c r="M42" s="160"/>
+      <c r="N42" s="160"/>
+      <c r="O42" s="160"/>
     </row>
     <row r="43" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="34"/>
@@ -5943,23 +6004,23 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="139" t="s">
+      <c r="A46" s="162" t="s">
         <v>215</v>
       </c>
-      <c r="B46" s="138"/>
-      <c r="C46" s="138"/>
-      <c r="D46" s="138"/>
-      <c r="E46" s="138"/>
-      <c r="F46" s="138"/>
-      <c r="G46" s="138"/>
-      <c r="H46" s="138"/>
-      <c r="I46" s="138"/>
-      <c r="J46" s="138"/>
-      <c r="K46" s="138"/>
-      <c r="L46" s="138"/>
-      <c r="M46" s="138"/>
-      <c r="N46" s="138"/>
-      <c r="O46" s="138"/>
+      <c r="B46" s="160"/>
+      <c r="C46" s="160"/>
+      <c r="D46" s="160"/>
+      <c r="E46" s="160"/>
+      <c r="F46" s="160"/>
+      <c r="G46" s="160"/>
+      <c r="H46" s="160"/>
+      <c r="I46" s="160"/>
+      <c r="J46" s="160"/>
+      <c r="K46" s="160"/>
+      <c r="L46" s="160"/>
+      <c r="M46" s="160"/>
+      <c r="N46" s="160"/>
+      <c r="O46" s="160"/>
     </row>
     <row r="47" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="38"/>
@@ -6361,23 +6422,23 @@
       </c>
     </row>
     <row r="54" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="139" t="s">
+      <c r="A54" s="162" t="s">
         <v>233</v>
       </c>
-      <c r="B54" s="138"/>
-      <c r="C54" s="138"/>
-      <c r="D54" s="138"/>
-      <c r="E54" s="138"/>
-      <c r="F54" s="138"/>
-      <c r="G54" s="138"/>
-      <c r="H54" s="138"/>
-      <c r="I54" s="138"/>
-      <c r="J54" s="138"/>
-      <c r="K54" s="138"/>
-      <c r="L54" s="138"/>
-      <c r="M54" s="138"/>
-      <c r="N54" s="138"/>
-      <c r="O54" s="138"/>
+      <c r="B54" s="160"/>
+      <c r="C54" s="160"/>
+      <c r="D54" s="160"/>
+      <c r="E54" s="160"/>
+      <c r="F54" s="160"/>
+      <c r="G54" s="160"/>
+      <c r="H54" s="160"/>
+      <c r="I54" s="160"/>
+      <c r="J54" s="160"/>
+      <c r="K54" s="160"/>
+      <c r="L54" s="160"/>
+      <c r="M54" s="160"/>
+      <c r="N54" s="160"/>
+      <c r="O54" s="160"/>
     </row>
     <row r="55" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="42"/>
@@ -6836,23 +6897,23 @@
       </c>
     </row>
     <row r="63" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="139" t="s">
+      <c r="A63" s="162" t="s">
         <v>261</v>
       </c>
-      <c r="B63" s="138"/>
-      <c r="C63" s="138"/>
-      <c r="D63" s="138"/>
-      <c r="E63" s="138"/>
-      <c r="F63" s="138"/>
-      <c r="G63" s="138"/>
-      <c r="H63" s="138"/>
-      <c r="I63" s="138"/>
-      <c r="J63" s="138"/>
-      <c r="K63" s="138"/>
-      <c r="L63" s="138"/>
-      <c r="M63" s="138"/>
-      <c r="N63" s="138"/>
-      <c r="O63" s="138"/>
+      <c r="B63" s="160"/>
+      <c r="C63" s="160"/>
+      <c r="D63" s="160"/>
+      <c r="E63" s="160"/>
+      <c r="F63" s="160"/>
+      <c r="G63" s="160"/>
+      <c r="H63" s="160"/>
+      <c r="I63" s="160"/>
+      <c r="J63" s="160"/>
+      <c r="K63" s="160"/>
+      <c r="L63" s="160"/>
+      <c r="M63" s="160"/>
+      <c r="N63" s="160"/>
+      <c r="O63" s="160"/>
     </row>
     <row r="64" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="47"/>
@@ -7197,23 +7258,23 @@
       </c>
     </row>
     <row r="70" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="139" t="s">
+      <c r="A70" s="162" t="s">
         <v>281</v>
       </c>
-      <c r="B70" s="138"/>
-      <c r="C70" s="138"/>
-      <c r="D70" s="138"/>
-      <c r="E70" s="138"/>
-      <c r="F70" s="138"/>
-      <c r="G70" s="138"/>
-      <c r="H70" s="138"/>
-      <c r="I70" s="138"/>
-      <c r="J70" s="138"/>
-      <c r="K70" s="138"/>
-      <c r="L70" s="138"/>
-      <c r="M70" s="138"/>
-      <c r="N70" s="138"/>
-      <c r="O70" s="138"/>
+      <c r="B70" s="160"/>
+      <c r="C70" s="160"/>
+      <c r="D70" s="160"/>
+      <c r="E70" s="160"/>
+      <c r="F70" s="160"/>
+      <c r="G70" s="160"/>
+      <c r="H70" s="160"/>
+      <c r="I70" s="160"/>
+      <c r="J70" s="160"/>
+      <c r="K70" s="160"/>
+      <c r="L70" s="160"/>
+      <c r="M70" s="160"/>
+      <c r="N70" s="160"/>
+      <c r="O70" s="160"/>
     </row>
     <row r="71" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="51"/>
@@ -7444,23 +7505,23 @@
       </c>
     </row>
     <row r="75" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="139" t="s">
+      <c r="A75" s="162" t="s">
         <v>294</v>
       </c>
-      <c r="B75" s="138"/>
-      <c r="C75" s="138"/>
-      <c r="D75" s="138"/>
-      <c r="E75" s="138"/>
-      <c r="F75" s="138"/>
-      <c r="G75" s="138"/>
-      <c r="H75" s="138"/>
-      <c r="I75" s="138"/>
-      <c r="J75" s="138"/>
-      <c r="K75" s="138"/>
-      <c r="L75" s="138"/>
-      <c r="M75" s="138"/>
-      <c r="N75" s="138"/>
-      <c r="O75" s="138"/>
+      <c r="B75" s="160"/>
+      <c r="C75" s="160"/>
+      <c r="D75" s="160"/>
+      <c r="E75" s="160"/>
+      <c r="F75" s="160"/>
+      <c r="G75" s="160"/>
+      <c r="H75" s="160"/>
+      <c r="I75" s="160"/>
+      <c r="J75" s="160"/>
+      <c r="K75" s="160"/>
+      <c r="L75" s="160"/>
+      <c r="M75" s="160"/>
+      <c r="N75" s="160"/>
+      <c r="O75" s="160"/>
     </row>
     <row r="76" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="55"/>
@@ -8318,23 +8379,23 @@
       </c>
     </row>
     <row r="91" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="139" t="s">
+      <c r="A91" s="162" t="s">
         <v>345</v>
       </c>
-      <c r="B91" s="138"/>
-      <c r="C91" s="138"/>
-      <c r="D91" s="138"/>
-      <c r="E91" s="138"/>
-      <c r="F91" s="138"/>
-      <c r="G91" s="138"/>
-      <c r="H91" s="138"/>
-      <c r="I91" s="138"/>
-      <c r="J91" s="138"/>
-      <c r="K91" s="138"/>
-      <c r="L91" s="138"/>
-      <c r="M91" s="138"/>
-      <c r="N91" s="138"/>
-      <c r="O91" s="138"/>
+      <c r="B91" s="160"/>
+      <c r="C91" s="160"/>
+      <c r="D91" s="160"/>
+      <c r="E91" s="160"/>
+      <c r="F91" s="160"/>
+      <c r="G91" s="160"/>
+      <c r="H91" s="160"/>
+      <c r="I91" s="160"/>
+      <c r="J91" s="160"/>
+      <c r="K91" s="160"/>
+      <c r="L91" s="160"/>
+      <c r="M91" s="160"/>
+      <c r="N91" s="160"/>
+      <c r="O91" s="160"/>
     </row>
     <row r="92" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="59"/>
@@ -8622,23 +8683,23 @@
       </c>
     </row>
     <row r="97" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="139" t="s">
+      <c r="A97" s="162" t="s">
         <v>361</v>
       </c>
-      <c r="B97" s="138"/>
-      <c r="C97" s="138"/>
-      <c r="D97" s="138"/>
-      <c r="E97" s="138"/>
-      <c r="F97" s="138"/>
-      <c r="G97" s="138"/>
-      <c r="H97" s="138"/>
-      <c r="I97" s="138"/>
-      <c r="J97" s="138"/>
-      <c r="K97" s="138"/>
-      <c r="L97" s="138"/>
-      <c r="M97" s="138"/>
-      <c r="N97" s="138"/>
-      <c r="O97" s="138"/>
+      <c r="B97" s="160"/>
+      <c r="C97" s="160"/>
+      <c r="D97" s="160"/>
+      <c r="E97" s="160"/>
+      <c r="F97" s="160"/>
+      <c r="G97" s="160"/>
+      <c r="H97" s="160"/>
+      <c r="I97" s="160"/>
+      <c r="J97" s="160"/>
+      <c r="K97" s="160"/>
+      <c r="L97" s="160"/>
+      <c r="M97" s="160"/>
+      <c r="N97" s="160"/>
+      <c r="O97" s="160"/>
     </row>
     <row r="98" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="63"/>
@@ -8926,23 +8987,23 @@
       </c>
     </row>
     <row r="103" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="139" t="s">
+      <c r="A103" s="162" t="s">
         <v>377</v>
       </c>
-      <c r="B103" s="138"/>
-      <c r="C103" s="138"/>
-      <c r="D103" s="138"/>
-      <c r="E103" s="138"/>
-      <c r="F103" s="138"/>
-      <c r="G103" s="138"/>
-      <c r="H103" s="138"/>
-      <c r="I103" s="138"/>
-      <c r="J103" s="138"/>
-      <c r="K103" s="138"/>
-      <c r="L103" s="138"/>
-      <c r="M103" s="138"/>
-      <c r="N103" s="138"/>
-      <c r="O103" s="138"/>
+      <c r="B103" s="160"/>
+      <c r="C103" s="160"/>
+      <c r="D103" s="160"/>
+      <c r="E103" s="160"/>
+      <c r="F103" s="160"/>
+      <c r="G103" s="160"/>
+      <c r="H103" s="160"/>
+      <c r="I103" s="160"/>
+      <c r="J103" s="160"/>
+      <c r="K103" s="160"/>
+      <c r="L103" s="160"/>
+      <c r="M103" s="160"/>
+      <c r="N103" s="160"/>
+      <c r="O103" s="160"/>
     </row>
     <row r="104" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="67"/>
@@ -9230,23 +9291,23 @@
       </c>
     </row>
     <row r="109" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="139" t="s">
+      <c r="A109" s="162" t="s">
         <v>393</v>
       </c>
-      <c r="B109" s="138"/>
-      <c r="C109" s="138"/>
-      <c r="D109" s="138"/>
-      <c r="E109" s="138"/>
-      <c r="F109" s="138"/>
-      <c r="G109" s="138"/>
-      <c r="H109" s="138"/>
-      <c r="I109" s="138"/>
-      <c r="J109" s="138"/>
-      <c r="K109" s="138"/>
-      <c r="L109" s="138"/>
-      <c r="M109" s="138"/>
-      <c r="N109" s="138"/>
-      <c r="O109" s="138"/>
+      <c r="B109" s="160"/>
+      <c r="C109" s="160"/>
+      <c r="D109" s="160"/>
+      <c r="E109" s="160"/>
+      <c r="F109" s="160"/>
+      <c r="G109" s="160"/>
+      <c r="H109" s="160"/>
+      <c r="I109" s="160"/>
+      <c r="J109" s="160"/>
+      <c r="K109" s="160"/>
+      <c r="L109" s="160"/>
+      <c r="M109" s="160"/>
+      <c r="N109" s="160"/>
+      <c r="O109" s="160"/>
     </row>
     <row r="110" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="71"/>
@@ -9534,23 +9595,23 @@
       </c>
     </row>
     <row r="115" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="139" t="s">
+      <c r="A115" s="162" t="s">
         <v>407</v>
       </c>
-      <c r="B115" s="138"/>
-      <c r="C115" s="138"/>
-      <c r="D115" s="138"/>
-      <c r="E115" s="138"/>
-      <c r="F115" s="138"/>
-      <c r="G115" s="138"/>
-      <c r="H115" s="138"/>
-      <c r="I115" s="138"/>
-      <c r="J115" s="138"/>
-      <c r="K115" s="138"/>
-      <c r="L115" s="138"/>
-      <c r="M115" s="138"/>
-      <c r="N115" s="138"/>
-      <c r="O115" s="138"/>
+      <c r="B115" s="160"/>
+      <c r="C115" s="160"/>
+      <c r="D115" s="160"/>
+      <c r="E115" s="160"/>
+      <c r="F115" s="160"/>
+      <c r="G115" s="160"/>
+      <c r="H115" s="160"/>
+      <c r="I115" s="160"/>
+      <c r="J115" s="160"/>
+      <c r="K115" s="160"/>
+      <c r="L115" s="160"/>
+      <c r="M115" s="160"/>
+      <c r="N115" s="160"/>
+      <c r="O115" s="160"/>
     </row>
     <row r="116" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="75"/>
@@ -9838,23 +9899,23 @@
       </c>
     </row>
     <row r="121" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="139" t="s">
+      <c r="A121" s="162" t="s">
         <v>424</v>
       </c>
-      <c r="B121" s="138"/>
-      <c r="C121" s="138"/>
-      <c r="D121" s="138"/>
-      <c r="E121" s="138"/>
-      <c r="F121" s="138"/>
-      <c r="G121" s="138"/>
-      <c r="H121" s="138"/>
-      <c r="I121" s="138"/>
-      <c r="J121" s="138"/>
-      <c r="K121" s="138"/>
-      <c r="L121" s="138"/>
-      <c r="M121" s="138"/>
-      <c r="N121" s="138"/>
-      <c r="O121" s="138"/>
+      <c r="B121" s="160"/>
+      <c r="C121" s="160"/>
+      <c r="D121" s="160"/>
+      <c r="E121" s="160"/>
+      <c r="F121" s="160"/>
+      <c r="G121" s="160"/>
+      <c r="H121" s="160"/>
+      <c r="I121" s="160"/>
+      <c r="J121" s="160"/>
+      <c r="K121" s="160"/>
+      <c r="L121" s="160"/>
+      <c r="M121" s="160"/>
+      <c r="N121" s="160"/>
+      <c r="O121" s="160"/>
     </row>
     <row r="122" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="79"/>
@@ -10199,23 +10260,23 @@
       </c>
     </row>
     <row r="128" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="139" t="s">
+      <c r="A128" s="162" t="s">
         <v>441</v>
       </c>
-      <c r="B128" s="138"/>
-      <c r="C128" s="138"/>
-      <c r="D128" s="138"/>
-      <c r="E128" s="138"/>
-      <c r="F128" s="138"/>
-      <c r="G128" s="138"/>
-      <c r="H128" s="138"/>
-      <c r="I128" s="138"/>
-      <c r="J128" s="138"/>
-      <c r="K128" s="138"/>
-      <c r="L128" s="138"/>
-      <c r="M128" s="138"/>
-      <c r="N128" s="138"/>
-      <c r="O128" s="138"/>
+      <c r="B128" s="160"/>
+      <c r="C128" s="160"/>
+      <c r="D128" s="160"/>
+      <c r="E128" s="160"/>
+      <c r="F128" s="160"/>
+      <c r="G128" s="160"/>
+      <c r="H128" s="160"/>
+      <c r="I128" s="160"/>
+      <c r="J128" s="160"/>
+      <c r="K128" s="160"/>
+      <c r="L128" s="160"/>
+      <c r="M128" s="160"/>
+      <c r="N128" s="160"/>
+      <c r="O128" s="160"/>
     </row>
     <row r="129" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="59"/>
@@ -10677,10 +10738,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A103:O103"/>
-    <mergeCell ref="A70:O70"/>
-    <mergeCell ref="A54:O54"/>
     <mergeCell ref="A128:O128"/>
     <mergeCell ref="A46:O46"/>
     <mergeCell ref="A75:O75"/>
@@ -10696,6 +10753,10 @@
     <mergeCell ref="A121:O121"/>
     <mergeCell ref="A115:O115"/>
     <mergeCell ref="A9:O9"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A103:O103"/>
+    <mergeCell ref="A70:O70"/>
+    <mergeCell ref="A54:O54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10718,16 +10779,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="137" t="s">
+      <c r="A1" s="161" t="s">
         <v>475</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160"/>
     </row>
     <row r="2" spans="1:10" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -11364,14 +11425,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="137" t="s">
+      <c r="A1" s="161" t="s">
         <v>543</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
     </row>
     <row r="2" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -11474,14 +11535,14 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="141" t="s">
+      <c r="A8" s="164" t="s">
         <v>569</v>
       </c>
-      <c r="B8" s="138"/>
-      <c r="C8" s="138"/>
-      <c r="D8" s="138"/>
-      <c r="E8" s="138"/>
-      <c r="F8" s="138"/>
+      <c r="B8" s="160"/>
+      <c r="C8" s="160"/>
+      <c r="D8" s="160"/>
+      <c r="E8" s="160"/>
+      <c r="F8" s="160"/>
     </row>
     <row r="10" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="115" t="s">
@@ -11514,1779 +11575,1878 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.1640625" style="143" customWidth="1"/>
-    <col min="2" max="3" width="8" style="143" customWidth="1"/>
-    <col min="4" max="4" width="44.1640625" style="143" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58" style="143" customWidth="1"/>
-    <col min="6" max="6" width="26" style="143" customWidth="1"/>
-    <col min="7" max="8" width="7" style="143" customWidth="1"/>
-    <col min="9" max="10" width="8" style="143" customWidth="1"/>
-    <col min="11" max="11" width="9" style="143" customWidth="1"/>
-    <col min="12" max="16384" width="8.83203125" style="143"/>
+    <col min="1" max="1" width="14.1640625" customWidth="1"/>
+    <col min="2" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="30.5" customWidth="1"/>
+    <col min="5" max="5" width="66.6640625" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="8" width="7" customWidth="1"/>
+    <col min="9" max="10" width="8" customWidth="1"/>
+    <col min="11" max="11" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="137" t="s">
         <v>573</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="144" t="s">
+      <c r="A2" s="159" t="s">
         <v>574</v>
       </c>
-      <c r="B2" s="145"/>
-      <c r="C2" s="145"/>
-      <c r="D2" s="145"/>
-      <c r="E2" s="145"/>
-      <c r="F2" s="145"/>
-      <c r="G2" s="145"/>
-      <c r="H2" s="145"/>
-      <c r="I2" s="145"/>
-      <c r="J2" s="145"/>
-      <c r="K2" s="145"/>
+      <c r="B2" s="160"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
     </row>
     <row r="4" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="150" t="s">
+      <c r="A4" s="142" t="s">
         <v>575</v>
       </c>
-      <c r="B4" s="150" t="s">
+      <c r="B4" s="142" t="s">
         <v>576</v>
       </c>
-      <c r="C4" s="150" t="s">
+      <c r="C4" s="142" t="s">
         <v>577</v>
       </c>
-      <c r="D4" s="150" t="s">
+      <c r="D4" s="142" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="150" t="s">
+      <c r="E4" s="142" t="s">
         <v>578</v>
       </c>
-      <c r="F4" s="150" t="s">
+      <c r="F4" s="142" t="s">
         <v>579</v>
       </c>
-      <c r="G4" s="150" t="s">
+      <c r="G4" s="142" t="s">
         <v>580</v>
       </c>
-      <c r="H4" s="150" t="s">
+      <c r="H4" s="142" t="s">
         <v>581</v>
       </c>
-      <c r="I4" s="150" t="s">
+      <c r="I4" s="142" t="s">
         <v>582</v>
       </c>
-      <c r="J4" s="150" t="s">
+      <c r="J4" s="142" t="s">
         <v>66</v>
       </c>
-      <c r="K4" s="150" t="s">
+      <c r="K4" s="142" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="151" t="s">
+      <c r="A5" s="143" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="146" t="s">
+      <c r="B5" s="138" t="s">
         <v>584</v>
       </c>
-      <c r="C5" s="146" t="s">
+      <c r="C5" s="138" t="s">
         <v>585</v>
       </c>
-      <c r="D5" s="147" t="s">
+      <c r="D5" s="139" t="s">
         <v>586</v>
       </c>
-      <c r="E5" s="148" t="s">
+      <c r="E5" s="140" t="s">
         <v>587</v>
       </c>
-      <c r="F5" s="147" t="s">
+      <c r="F5" s="139" t="s">
         <v>588</v>
       </c>
-      <c r="G5" s="146">
+      <c r="G5" s="138">
         <v>2</v>
       </c>
-      <c r="H5" s="146">
-        <v>1</v>
-      </c>
-      <c r="I5" s="146">
+      <c r="H5" s="138">
+        <v>1</v>
+      </c>
+      <c r="I5" s="138">
         <v>3</v>
       </c>
-      <c r="J5" s="146" t="s">
+      <c r="J5" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K5" s="146">
+      <c r="K5" s="138">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="151" t="s">
+      <c r="A6" s="143" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="146" t="s">
+      <c r="B6" s="138" t="s">
         <v>584</v>
       </c>
-      <c r="C6" s="146" t="s">
+      <c r="C6" s="138" t="s">
         <v>585</v>
       </c>
-      <c r="D6" s="147" t="s">
+      <c r="D6" s="139" t="s">
         <v>586</v>
       </c>
-      <c r="E6" s="148" t="s">
+      <c r="E6" s="140" t="s">
         <v>589</v>
       </c>
-      <c r="F6" s="147" t="s">
+      <c r="F6" s="139" t="s">
         <v>588</v>
       </c>
-      <c r="G6" s="146">
-        <v>1</v>
-      </c>
-      <c r="H6" s="146">
+      <c r="G6" s="138">
+        <v>1</v>
+      </c>
+      <c r="H6" s="138">
         <v>0.5</v>
       </c>
-      <c r="I6" s="146">
+      <c r="I6" s="138">
         <v>1.5</v>
       </c>
-      <c r="J6" s="146" t="s">
+      <c r="J6" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K6" s="146">
+      <c r="K6" s="138">
         <v>4.5</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="151" t="s">
+      <c r="A7" s="143" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="146" t="s">
+      <c r="B7" s="138" t="s">
         <v>584</v>
       </c>
-      <c r="C7" s="146" t="s">
+      <c r="C7" s="138" t="s">
         <v>585</v>
       </c>
-      <c r="D7" s="147" t="s">
+      <c r="D7" s="139" t="s">
         <v>590</v>
       </c>
-      <c r="E7" s="148" t="s">
+      <c r="E7" s="140" t="s">
         <v>591</v>
       </c>
-      <c r="F7" s="147" t="s">
+      <c r="F7" s="139" t="s">
         <v>588</v>
       </c>
-      <c r="G7" s="146">
-        <v>1</v>
-      </c>
-      <c r="H7" s="146">
-        <v>1</v>
-      </c>
-      <c r="I7" s="146">
+      <c r="G7" s="138">
+        <v>1</v>
+      </c>
+      <c r="H7" s="138">
+        <v>1</v>
+      </c>
+      <c r="I7" s="138">
         <v>2</v>
       </c>
-      <c r="J7" s="146" t="s">
+      <c r="J7" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K7" s="146">
+      <c r="K7" s="138">
         <v>6.5</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="151" t="s">
+      <c r="A8" s="143" t="s">
         <v>88</v>
       </c>
-      <c r="B8" s="146" t="s">
+      <c r="B8" s="138" t="s">
         <v>584</v>
       </c>
-      <c r="C8" s="146" t="s">
+      <c r="C8" s="138" t="s">
         <v>585</v>
       </c>
-      <c r="D8" s="147" t="s">
+      <c r="D8" s="139" t="s">
         <v>592</v>
       </c>
-      <c r="E8" s="148" t="s">
+      <c r="E8" s="140" t="s">
         <v>593</v>
       </c>
-      <c r="F8" s="147" t="s">
+      <c r="F8" s="139" t="s">
         <v>669</v>
       </c>
-      <c r="G8" s="146">
-        <v>1</v>
-      </c>
-      <c r="H8" s="146">
-        <v>1</v>
-      </c>
-      <c r="I8" s="146">
+      <c r="G8" s="138">
+        <v>1</v>
+      </c>
+      <c r="H8" s="138">
+        <v>1</v>
+      </c>
+      <c r="I8" s="138">
         <v>2</v>
       </c>
-      <c r="J8" s="146" t="s">
+      <c r="J8" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K8" s="146">
+      <c r="K8" s="138">
         <v>8.5</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="151" t="s">
+      <c r="A9" s="143" t="s">
         <v>88</v>
       </c>
-      <c r="B9" s="146" t="s">
+      <c r="B9" s="138" t="s">
         <v>584</v>
       </c>
-      <c r="C9" s="146" t="s">
+      <c r="C9" s="138" t="s">
         <v>585</v>
       </c>
-      <c r="D9" s="147" t="s">
+      <c r="D9" s="139" t="s">
         <v>595</v>
       </c>
-      <c r="E9" s="148" t="s">
+      <c r="E9" s="140" t="s">
         <v>596</v>
       </c>
-      <c r="F9" s="147" t="s">
+      <c r="F9" s="139" t="s">
         <v>669</v>
       </c>
-      <c r="G9" s="146">
+      <c r="G9" s="138">
         <v>0.5</v>
       </c>
-      <c r="H9" s="146">
-        <v>1</v>
-      </c>
-      <c r="I9" s="146">
+      <c r="H9" s="138">
+        <v>1</v>
+      </c>
+      <c r="I9" s="138">
         <v>1.5</v>
       </c>
-      <c r="J9" s="146" t="s">
+      <c r="J9" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K9" s="146">
+      <c r="K9" s="138">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="151" t="s">
+      <c r="A10" s="143" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="146" t="s">
+      <c r="B10" s="138" t="s">
         <v>584</v>
       </c>
-      <c r="C10" s="146" t="s">
+      <c r="C10" s="138" t="s">
         <v>585</v>
       </c>
-      <c r="D10" s="147" t="s">
+      <c r="D10" s="139" t="s">
         <v>597</v>
       </c>
-      <c r="E10" s="148" t="s">
+      <c r="E10" s="140" t="s">
         <v>598</v>
       </c>
-      <c r="F10" s="147" t="s">
+      <c r="F10" s="139" t="s">
         <v>669</v>
       </c>
-      <c r="G10" s="146">
+      <c r="G10" s="138">
         <v>0.5</v>
       </c>
-      <c r="H10" s="146">
+      <c r="H10" s="138">
         <v>0.5</v>
       </c>
-      <c r="I10" s="146">
-        <v>1</v>
-      </c>
-      <c r="J10" s="146" t="s">
+      <c r="I10" s="138">
+        <v>1</v>
+      </c>
+      <c r="J10" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K10" s="146">
+      <c r="K10" s="138">
         <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="151" t="s">
+      <c r="A11" s="143" t="s">
         <v>88</v>
       </c>
-      <c r="B11" s="146" t="s">
+      <c r="B11" s="138" t="s">
         <v>584</v>
       </c>
-      <c r="C11" s="146" t="s">
+      <c r="C11" s="138" t="s">
         <v>585</v>
       </c>
-      <c r="D11" s="147" t="s">
+      <c r="D11" s="139" t="s">
         <v>599</v>
       </c>
-      <c r="E11" s="148" t="s">
+      <c r="E11" s="140" t="s">
         <v>600</v>
       </c>
-      <c r="F11" s="147" t="s">
+      <c r="F11" s="139" t="s">
         <v>669</v>
       </c>
-      <c r="G11" s="146">
+      <c r="G11" s="138">
         <v>0.5</v>
       </c>
-      <c r="H11" s="146">
+      <c r="H11" s="138">
         <v>0.5</v>
       </c>
-      <c r="I11" s="146">
-        <v>1</v>
-      </c>
-      <c r="J11" s="146" t="s">
+      <c r="I11" s="138">
+        <v>1</v>
+      </c>
+      <c r="J11" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K11" s="146">
+      <c r="K11" s="138">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="151" t="s">
+      <c r="A12" s="143" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="146" t="s">
+      <c r="B12" s="138" t="s">
         <v>584</v>
       </c>
-      <c r="C12" s="146" t="s">
+      <c r="C12" s="138" t="s">
         <v>585</v>
       </c>
-      <c r="D12" s="147" t="s">
+      <c r="D12" s="139" t="s">
         <v>509</v>
       </c>
-      <c r="E12" s="148" t="s">
+      <c r="E12" s="140" t="s">
         <v>601</v>
       </c>
-      <c r="F12" s="147" t="s">
+      <c r="F12" s="139" t="s">
         <v>669</v>
       </c>
-      <c r="G12" s="146">
+      <c r="G12" s="138">
         <v>0.5</v>
       </c>
-      <c r="H12" s="146">
+      <c r="H12" s="138">
         <v>0.5</v>
       </c>
-      <c r="I12" s="146">
-        <v>1</v>
-      </c>
-      <c r="J12" s="146" t="s">
+      <c r="I12" s="138">
+        <v>1</v>
+      </c>
+      <c r="J12" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K12" s="146">
+      <c r="K12" s="138">
         <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="151" t="s">
+      <c r="A13" s="143" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="146" t="s">
+      <c r="B13" s="138" t="s">
         <v>584</v>
       </c>
-      <c r="C13" s="146" t="s">
+      <c r="C13" s="138" t="s">
         <v>585</v>
       </c>
-      <c r="D13" s="147" t="s">
+      <c r="D13" s="139" t="s">
         <v>602</v>
       </c>
-      <c r="E13" s="148" t="s">
+      <c r="E13" s="140" t="s">
         <v>603</v>
       </c>
-      <c r="F13" s="147" t="s">
+      <c r="F13" s="139" t="s">
         <v>669</v>
       </c>
-      <c r="G13" s="146">
-        <v>1</v>
-      </c>
-      <c r="H13" s="146">
-        <v>1</v>
-      </c>
-      <c r="I13" s="146">
+      <c r="G13" s="138">
+        <v>1</v>
+      </c>
+      <c r="H13" s="138">
+        <v>1</v>
+      </c>
+      <c r="I13" s="138">
         <v>2</v>
       </c>
-      <c r="J13" s="146" t="s">
+      <c r="J13" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K13" s="146">
+      <c r="K13" s="138">
         <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="151" t="s">
+      <c r="A14" s="143" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="146" t="s">
+      <c r="B14" s="138" t="s">
         <v>584</v>
       </c>
-      <c r="C14" s="146" t="s">
+      <c r="C14" s="138" t="s">
         <v>585</v>
       </c>
-      <c r="D14" s="147" t="s">
+      <c r="D14" s="139" t="s">
         <v>604</v>
       </c>
-      <c r="E14" s="148" t="s">
+      <c r="E14" s="140" t="s">
         <v>605</v>
       </c>
-      <c r="F14" s="147" t="s">
+      <c r="F14" s="139" t="s">
         <v>669</v>
       </c>
-      <c r="G14" s="146">
+      <c r="G14" s="138">
         <v>0.5</v>
       </c>
-      <c r="H14" s="146">
+      <c r="H14" s="138">
         <v>0.5</v>
       </c>
-      <c r="I14" s="146">
-        <v>1</v>
-      </c>
-      <c r="J14" s="146" t="s">
+      <c r="I14" s="138">
+        <v>1</v>
+      </c>
+      <c r="J14" s="138" t="s">
         <v>116</v>
       </c>
-      <c r="K14" s="146">
+      <c r="K14" s="138">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="151" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" s="156" t="s">
+        <v>700</v>
+      </c>
+      <c r="B15" s="157"/>
+      <c r="C15" s="157"/>
+      <c r="D15" s="157"/>
+      <c r="E15" s="157"/>
+      <c r="F15" s="157"/>
+      <c r="G15" s="157"/>
+      <c r="H15" s="157"/>
+      <c r="I15" s="157"/>
+      <c r="J15" s="157"/>
+      <c r="K15" s="158"/>
+    </row>
+    <row r="16" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="143" t="s">
         <v>119</v>
       </c>
-      <c r="B15" s="146" t="s">
+      <c r="B16" s="138" t="s">
         <v>606</v>
       </c>
-      <c r="C15" s="146" t="s">
+      <c r="C16" s="138" t="s">
         <v>607</v>
       </c>
-      <c r="D15" s="147" t="s">
+      <c r="D16" s="139" t="s">
         <v>608</v>
       </c>
-      <c r="E15" s="148" t="s">
+      <c r="E16" s="140" t="s">
         <v>609</v>
       </c>
-      <c r="F15" s="147" t="s">
+      <c r="F16" s="139" t="s">
         <v>669</v>
       </c>
-      <c r="G15" s="146">
-        <v>1</v>
-      </c>
-      <c r="H15" s="146">
+      <c r="G16" s="138">
+        <v>1</v>
+      </c>
+      <c r="H16" s="138">
         <v>0.5</v>
       </c>
-      <c r="I15" s="146">
+      <c r="I16" s="138">
         <v>1.5</v>
       </c>
-      <c r="J15" s="146" t="s">
+      <c r="J16" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K15" s="146">
+      <c r="K16" s="138">
         <v>17.5</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A16" s="151" t="s">
+    <row r="17" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A17" s="143" t="s">
         <v>119</v>
       </c>
-      <c r="B16" s="146" t="s">
+      <c r="B17" s="138" t="s">
         <v>606</v>
       </c>
-      <c r="C16" s="146" t="s">
+      <c r="C17" s="138" t="s">
         <v>607</v>
       </c>
-      <c r="D16" s="147" t="s">
+      <c r="D17" s="139" t="s">
         <v>610</v>
       </c>
-      <c r="E16" s="148" t="s">
+      <c r="E17" s="140" t="s">
         <v>611</v>
       </c>
-      <c r="F16" s="147" t="s">
+      <c r="F17" s="139" t="s">
         <v>669</v>
       </c>
-      <c r="G16" s="146">
+      <c r="G17" s="138">
         <v>0.5</v>
       </c>
-      <c r="H16" s="146">
-        <v>1</v>
-      </c>
-      <c r="I16" s="146">
+      <c r="H17" s="138">
+        <v>1</v>
+      </c>
+      <c r="I17" s="138">
         <v>1.5</v>
       </c>
-      <c r="J16" s="146" t="s">
+      <c r="J17" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K16" s="146">
+      <c r="K17" s="138">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="151" t="s">
+    <row r="18" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="143" t="s">
         <v>119</v>
       </c>
-      <c r="B17" s="146" t="s">
+      <c r="B18" s="138" t="s">
         <v>606</v>
       </c>
-      <c r="C17" s="146" t="s">
+      <c r="C18" s="138" t="s">
         <v>607</v>
       </c>
-      <c r="D17" s="147" t="s">
+      <c r="D18" s="139" t="s">
         <v>608</v>
       </c>
-      <c r="E17" s="148" t="s">
+      <c r="E18" s="140" t="s">
         <v>612</v>
       </c>
-      <c r="F17" s="147" t="s">
+      <c r="F18" s="139" t="s">
         <v>669</v>
       </c>
-      <c r="G17" s="146">
+      <c r="G18" s="138">
         <v>0.5</v>
       </c>
-      <c r="H17" s="146">
+      <c r="H18" s="138">
         <v>1.5</v>
       </c>
-      <c r="I17" s="146">
+      <c r="I18" s="138">
         <v>2</v>
       </c>
-      <c r="J17" s="146" t="s">
+      <c r="J18" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K17" s="146">
+      <c r="K18" s="138">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A18" s="151" t="s">
+    <row r="19" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="143" t="s">
         <v>119</v>
       </c>
-      <c r="B18" s="146" t="s">
+      <c r="B19" s="138" t="s">
         <v>606</v>
       </c>
-      <c r="C18" s="146" t="s">
+      <c r="C19" s="138" t="s">
         <v>607</v>
       </c>
-      <c r="D18" s="147" t="s">
+      <c r="D19" s="139" t="s">
         <v>613</v>
       </c>
-      <c r="E18" s="148" t="s">
+      <c r="E19" s="140" t="s">
         <v>614</v>
       </c>
-      <c r="F18" s="147" t="s">
+      <c r="F19" s="139" t="s">
         <v>669</v>
       </c>
-      <c r="G18" s="146">
+      <c r="G19" s="138">
         <v>0.5</v>
       </c>
-      <c r="H18" s="146">
+      <c r="H19" s="138">
         <v>1.5</v>
       </c>
-      <c r="I18" s="146">
+      <c r="I19" s="138">
         <v>2</v>
       </c>
-      <c r="J18" s="146" t="s">
+      <c r="J19" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K18" s="146">
+      <c r="K19" s="138">
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" s="151" t="s">
+    <row r="20" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="143" t="s">
         <v>119</v>
       </c>
-      <c r="B19" s="146" t="s">
+      <c r="B20" s="138" t="s">
         <v>606</v>
       </c>
-      <c r="C19" s="146" t="s">
+      <c r="C20" s="138" t="s">
         <v>607</v>
       </c>
-      <c r="D19" s="147" t="s">
+      <c r="D20" s="139" t="s">
         <v>592</v>
       </c>
-      <c r="E19" s="148" t="s">
+      <c r="E20" s="140" t="s">
         <v>615</v>
       </c>
-      <c r="F19" s="147" t="s">
+      <c r="F20" s="139" t="s">
         <v>669</v>
       </c>
-      <c r="G19" s="146">
+      <c r="G20" s="138">
         <v>0.5</v>
       </c>
-      <c r="H19" s="146">
+      <c r="H20" s="138">
         <v>0.5</v>
       </c>
-      <c r="I19" s="146">
-        <v>1</v>
-      </c>
-      <c r="J19" s="146" t="s">
+      <c r="I20" s="138">
+        <v>1</v>
+      </c>
+      <c r="J20" s="138" t="s">
         <v>116</v>
       </c>
-      <c r="K19" s="146">
+      <c r="K20" s="138">
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A20" s="151" t="s">
+    <row r="21" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A21" s="143" t="s">
         <v>119</v>
       </c>
-      <c r="B20" s="146" t="s">
+      <c r="B21" s="138" t="s">
         <v>606</v>
       </c>
-      <c r="C20" s="146" t="s">
+      <c r="C21" s="138" t="s">
         <v>607</v>
       </c>
-      <c r="D20" s="147" t="s">
+      <c r="D21" s="139" t="s">
         <v>616</v>
       </c>
-      <c r="E20" s="148" t="s">
+      <c r="E21" s="140" t="s">
         <v>617</v>
       </c>
-      <c r="F20" s="147" t="s">
+      <c r="F21" s="139" t="s">
         <v>669</v>
       </c>
-      <c r="G20" s="146">
+      <c r="G21" s="138">
         <v>0.5</v>
       </c>
-      <c r="H20" s="146">
+      <c r="H21" s="138">
         <v>0.5</v>
       </c>
-      <c r="I20" s="146">
-        <v>1</v>
-      </c>
-      <c r="J20" s="146" t="s">
+      <c r="I21" s="138">
+        <v>1</v>
+      </c>
+      <c r="J21" s="138" t="s">
         <v>116</v>
       </c>
-      <c r="K20" s="146">
+      <c r="K21" s="138">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="152" t="s">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="156"/>
+      <c r="B22" s="157"/>
+      <c r="C22" s="157"/>
+      <c r="D22" s="157"/>
+      <c r="E22" s="157"/>
+      <c r="F22" s="157"/>
+      <c r="G22" s="157"/>
+      <c r="H22" s="157"/>
+      <c r="I22" s="157"/>
+      <c r="J22" s="157"/>
+      <c r="K22" s="158"/>
+    </row>
+    <row r="23" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="144" t="s">
         <v>311</v>
       </c>
-      <c r="B21" s="146" t="s">
+      <c r="B23" s="138" t="s">
         <v>618</v>
       </c>
-      <c r="C21" s="146" t="s">
+      <c r="C23" s="138" t="s">
         <v>619</v>
       </c>
-      <c r="D21" s="147" t="s">
+      <c r="D23" s="139" t="s">
         <v>608</v>
       </c>
-      <c r="E21" s="148" t="s">
+      <c r="E23" s="140" t="s">
         <v>620</v>
       </c>
-      <c r="F21" s="147" t="s">
+      <c r="F23" s="139" t="s">
         <v>669</v>
       </c>
-      <c r="G21" s="146">
-        <v>1</v>
-      </c>
-      <c r="H21" s="146">
+      <c r="G23" s="138">
+        <v>1</v>
+      </c>
+      <c r="H23" s="138">
         <v>0.5</v>
       </c>
-      <c r="I21" s="146">
+      <c r="I23" s="138">
         <v>1.5</v>
       </c>
-      <c r="J21" s="146" t="s">
+      <c r="J23" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K21" s="146">
+      <c r="K23" s="138">
         <v>26.5</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="152" t="s">
+    <row r="24" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="144" t="s">
         <v>311</v>
       </c>
-      <c r="B22" s="146" t="s">
+      <c r="B24" s="138" t="s">
         <v>618</v>
       </c>
-      <c r="C22" s="146" t="s">
+      <c r="C24" s="138" t="s">
         <v>619</v>
       </c>
-      <c r="D22" s="147" t="s">
+      <c r="D24" s="139" t="s">
         <v>608</v>
       </c>
-      <c r="E22" s="148" t="s">
+      <c r="E24" s="140" t="s">
         <v>621</v>
       </c>
-      <c r="F22" s="147" t="s">
+      <c r="F24" s="139" t="s">
         <v>669</v>
       </c>
-      <c r="G22" s="146">
+      <c r="G24" s="138">
         <v>1.5</v>
       </c>
-      <c r="H22" s="146">
+      <c r="H24" s="138">
         <v>0.5</v>
       </c>
-      <c r="I22" s="146">
+      <c r="I24" s="138">
         <v>2</v>
       </c>
-      <c r="J22" s="146" t="s">
+      <c r="J24" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K22" s="146">
+      <c r="K24" s="138">
         <v>28.5</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A23" s="152" t="s">
+    <row r="25" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="144" t="s">
         <v>311</v>
       </c>
-      <c r="B23" s="146" t="s">
+      <c r="B25" s="138" t="s">
         <v>618</v>
       </c>
-      <c r="C23" s="146" t="s">
+      <c r="C25" s="138" t="s">
         <v>619</v>
       </c>
-      <c r="D23" s="147" t="s">
+      <c r="D25" s="139" t="s">
         <v>608</v>
       </c>
-      <c r="E23" s="148" t="s">
+      <c r="E25" s="140" t="s">
         <v>622</v>
       </c>
-      <c r="F23" s="147" t="s">
+      <c r="F25" s="139" t="s">
         <v>669</v>
       </c>
-      <c r="G23" s="146">
+      <c r="G25" s="138">
         <v>1.5</v>
       </c>
-      <c r="H23" s="146">
+      <c r="H25" s="138">
         <v>0.5</v>
       </c>
-      <c r="I23" s="146">
+      <c r="I25" s="138">
         <v>2</v>
       </c>
-      <c r="J23" s="146" t="s">
+      <c r="J25" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K23" s="146">
+      <c r="K25" s="138">
         <v>30.5</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A24" s="152" t="s">
+    <row r="26" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" s="144" t="s">
         <v>311</v>
       </c>
-      <c r="B24" s="146" t="s">
+      <c r="B26" s="138" t="s">
         <v>618</v>
       </c>
-      <c r="C24" s="146" t="s">
+      <c r="C26" s="138" t="s">
         <v>619</v>
       </c>
-      <c r="D24" s="147" t="s">
+      <c r="D26" s="139" t="s">
         <v>608</v>
       </c>
-      <c r="E24" s="148" t="s">
+      <c r="E26" s="140" t="s">
         <v>623</v>
       </c>
-      <c r="F24" s="147" t="s">
+      <c r="F26" s="139" t="s">
         <v>669</v>
       </c>
-      <c r="G24" s="146">
-        <v>1</v>
-      </c>
-      <c r="H24" s="146">
+      <c r="G26" s="138">
+        <v>1</v>
+      </c>
+      <c r="H26" s="138">
         <v>0.5</v>
       </c>
-      <c r="I24" s="146">
+      <c r="I26" s="138">
         <v>1.5</v>
       </c>
-      <c r="J24" s="146" t="s">
+      <c r="J26" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K24" s="146">
+      <c r="K26" s="138">
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A25" s="152" t="s">
+    <row r="27" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="144" t="s">
         <v>311</v>
       </c>
-      <c r="B25" s="146" t="s">
+      <c r="B27" s="138" t="s">
         <v>618</v>
       </c>
-      <c r="C25" s="146" t="s">
+      <c r="C27" s="138" t="s">
         <v>619</v>
       </c>
-      <c r="D25" s="147" t="s">
+      <c r="D27" s="139" t="s">
         <v>608</v>
       </c>
-      <c r="E25" s="148" t="s">
+      <c r="E27" s="140" t="s">
         <v>624</v>
       </c>
-      <c r="F25" s="147" t="s">
+      <c r="F27" s="139" t="s">
         <v>669</v>
       </c>
-      <c r="G25" s="146">
-        <v>1</v>
-      </c>
-      <c r="H25" s="146">
+      <c r="G27" s="138">
+        <v>1</v>
+      </c>
+      <c r="H27" s="138">
         <v>0.5</v>
       </c>
-      <c r="I25" s="146">
+      <c r="I27" s="138">
         <v>1.5</v>
       </c>
-      <c r="J25" s="146" t="s">
+      <c r="J27" s="138" t="s">
         <v>116</v>
       </c>
-      <c r="K25" s="146">
+      <c r="K27" s="138">
         <v>33.5</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A26" s="152" t="s">
+    <row r="28" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="144" t="s">
         <v>311</v>
       </c>
-      <c r="B26" s="146" t="s">
+      <c r="B28" s="138" t="s">
         <v>618</v>
       </c>
-      <c r="C26" s="146" t="s">
+      <c r="C28" s="138" t="s">
         <v>619</v>
       </c>
-      <c r="D26" s="147" t="s">
+      <c r="D28" s="139" t="s">
         <v>625</v>
       </c>
-      <c r="E26" s="148" t="s">
+      <c r="E28" s="140" t="s">
         <v>626</v>
       </c>
-      <c r="F26" s="147" t="s">
+      <c r="F28" s="139" t="s">
         <v>669</v>
       </c>
-      <c r="G26" s="146">
+      <c r="G28" s="138">
         <v>0.5</v>
       </c>
-      <c r="H26" s="146">
-        <v>1</v>
-      </c>
-      <c r="I26" s="146">
+      <c r="H28" s="138">
+        <v>1</v>
+      </c>
+      <c r="I28" s="138">
         <v>1.5</v>
       </c>
-      <c r="J26" s="146" t="s">
+      <c r="J28" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K26" s="146">
+      <c r="K28" s="138">
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A27" s="152" t="s">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" s="156"/>
+      <c r="B29" s="157"/>
+      <c r="C29" s="157"/>
+      <c r="D29" s="157"/>
+      <c r="E29" s="157"/>
+      <c r="F29" s="157"/>
+      <c r="G29" s="157"/>
+      <c r="H29" s="157"/>
+      <c r="I29" s="157"/>
+      <c r="J29" s="157"/>
+      <c r="K29" s="158"/>
+    </row>
+    <row r="30" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="144" t="s">
         <v>158</v>
       </c>
-      <c r="B27" s="146" t="s">
+      <c r="B30" s="138" t="s">
         <v>627</v>
       </c>
-      <c r="C27" s="146" t="s">
+      <c r="C30" s="138" t="s">
         <v>628</v>
       </c>
-      <c r="D27" s="147" t="s">
+      <c r="D30" s="139" t="s">
         <v>629</v>
       </c>
-      <c r="E27" s="148" t="s">
+      <c r="E30" s="140" t="s">
         <v>630</v>
       </c>
-      <c r="F27" s="147" t="s">
+      <c r="F30" s="139" t="s">
         <v>669</v>
       </c>
-      <c r="G27" s="146">
+      <c r="G30" s="138">
         <v>3</v>
       </c>
-      <c r="H27" s="146">
-        <v>1</v>
-      </c>
-      <c r="I27" s="146">
+      <c r="H30" s="138">
+        <v>1</v>
+      </c>
+      <c r="I30" s="138">
         <v>4</v>
       </c>
-      <c r="J27" s="146" t="s">
+      <c r="J30" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K27" s="146">
+      <c r="K30" s="138">
         <v>39</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A28" s="152" t="s">
+    <row r="31" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" s="144" t="s">
         <v>158</v>
       </c>
-      <c r="B28" s="146" t="s">
+      <c r="B31" s="138" t="s">
         <v>627</v>
       </c>
-      <c r="C28" s="146" t="s">
+      <c r="C31" s="138" t="s">
         <v>628</v>
       </c>
-      <c r="D28" s="147" t="s">
+      <c r="D31" s="139" t="s">
         <v>613</v>
       </c>
-      <c r="E28" s="148" t="s">
+      <c r="E31" s="140" t="s">
         <v>631</v>
       </c>
-      <c r="F28" s="147" t="s">
+      <c r="F31" s="139" t="s">
         <v>669</v>
       </c>
-      <c r="G28" s="146">
-        <v>1</v>
-      </c>
-      <c r="H28" s="146">
+      <c r="G31" s="138">
+        <v>1</v>
+      </c>
+      <c r="H31" s="138">
         <v>0.5</v>
       </c>
-      <c r="I28" s="146">
+      <c r="I31" s="138">
         <v>1.5</v>
       </c>
-      <c r="J28" s="146" t="s">
+      <c r="J31" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K28" s="146">
+      <c r="K31" s="138">
         <v>40.5</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A29" s="152" t="s">
+    <row r="32" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" s="144" t="s">
         <v>158</v>
       </c>
-      <c r="B29" s="146" t="s">
+      <c r="B32" s="138" t="s">
         <v>627</v>
       </c>
-      <c r="C29" s="146" t="s">
+      <c r="C32" s="138" t="s">
         <v>628</v>
       </c>
-      <c r="D29" s="147" t="s">
+      <c r="D32" s="139" t="s">
         <v>509</v>
       </c>
-      <c r="E29" s="148" t="s">
+      <c r="E32" s="140" t="s">
         <v>632</v>
       </c>
-      <c r="F29" s="147" t="s">
+      <c r="F32" s="139" t="s">
         <v>669</v>
       </c>
-      <c r="G29" s="146">
+      <c r="G32" s="138">
         <v>1.5</v>
       </c>
-      <c r="H29" s="146">
+      <c r="H32" s="138">
         <v>0.5</v>
       </c>
-      <c r="I29" s="146">
+      <c r="I32" s="138">
         <v>2</v>
       </c>
-      <c r="J29" s="146" t="s">
+      <c r="J32" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K29" s="146">
+      <c r="K32" s="138">
         <v>42.5</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A30" s="152" t="s">
+    <row r="33" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="144" t="s">
         <v>158</v>
       </c>
-      <c r="B30" s="146" t="s">
+      <c r="B33" s="138" t="s">
         <v>627</v>
       </c>
-      <c r="C30" s="146" t="s">
+      <c r="C33" s="138" t="s">
         <v>628</v>
       </c>
-      <c r="D30" s="147" t="s">
+      <c r="D33" s="139" t="s">
         <v>599</v>
       </c>
-      <c r="E30" s="148" t="s">
+      <c r="E33" s="140" t="s">
         <v>633</v>
       </c>
-      <c r="F30" s="147" t="s">
+      <c r="F33" s="139" t="s">
         <v>669</v>
       </c>
-      <c r="G30" s="146">
+      <c r="G33" s="138">
         <v>2</v>
       </c>
-      <c r="H30" s="146">
-        <v>1</v>
-      </c>
-      <c r="I30" s="146">
+      <c r="H33" s="138">
+        <v>1</v>
+      </c>
+      <c r="I33" s="138">
         <v>3</v>
       </c>
-      <c r="J30" s="146" t="s">
+      <c r="J33" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K30" s="146">
+      <c r="K33" s="138">
         <v>45.5</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A31" s="153" t="s">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" s="156"/>
+      <c r="B34" s="157"/>
+      <c r="C34" s="157"/>
+      <c r="D34" s="157"/>
+      <c r="E34" s="157"/>
+      <c r="F34" s="157"/>
+      <c r="G34" s="157"/>
+      <c r="H34" s="157"/>
+      <c r="I34" s="157"/>
+      <c r="J34" s="157"/>
+      <c r="K34" s="158"/>
+    </row>
+    <row r="35" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="145" t="s">
         <v>350</v>
       </c>
-      <c r="B31" s="146" t="s">
+      <c r="B35" s="138" t="s">
         <v>634</v>
       </c>
-      <c r="C31" s="146" t="s">
+      <c r="C35" s="138" t="s">
         <v>635</v>
       </c>
-      <c r="D31" s="147" t="s">
+      <c r="D35" s="139" t="s">
         <v>636</v>
       </c>
-      <c r="E31" s="148" t="s">
+      <c r="E35" s="140" t="s">
         <v>637</v>
       </c>
-      <c r="F31" s="147" t="s">
+      <c r="F35" s="139" t="s">
         <v>638</v>
       </c>
-      <c r="G31" s="146">
+      <c r="G35" s="138">
         <v>0.5</v>
       </c>
-      <c r="H31" s="146">
+      <c r="H35" s="138">
         <v>0</v>
       </c>
-      <c r="I31" s="146">
+      <c r="I35" s="138">
         <v>0.5</v>
       </c>
-      <c r="J31" s="146" t="s">
+      <c r="J35" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K31" s="146">
+      <c r="K35" s="138">
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="153" t="s">
+    <row r="36" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A36" s="145" t="s">
         <v>350</v>
       </c>
-      <c r="B32" s="146" t="s">
+      <c r="B36" s="138" t="s">
         <v>634</v>
       </c>
-      <c r="C32" s="146" t="s">
+      <c r="C36" s="138" t="s">
         <v>635</v>
       </c>
-      <c r="D32" s="147" t="s">
+      <c r="D36" s="139" t="s">
         <v>636</v>
       </c>
-      <c r="E32" s="148" t="s">
+      <c r="E36" s="140" t="s">
         <v>639</v>
       </c>
-      <c r="F32" s="147" t="s">
+      <c r="F36" s="139" t="s">
         <v>640</v>
       </c>
-      <c r="G32" s="146">
+      <c r="G36" s="138">
         <v>3</v>
       </c>
-      <c r="H32" s="146">
-        <v>1</v>
-      </c>
-      <c r="I32" s="146">
+      <c r="H36" s="138">
+        <v>1</v>
+      </c>
+      <c r="I36" s="138">
         <v>4</v>
       </c>
-      <c r="J32" s="146" t="s">
+      <c r="J36" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K32" s="146">
+      <c r="K36" s="138">
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="153" t="s">
+    <row r="37" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" s="145" t="s">
         <v>350</v>
       </c>
-      <c r="B33" s="146" t="s">
+      <c r="B37" s="138" t="s">
         <v>634</v>
       </c>
-      <c r="C33" s="146" t="s">
+      <c r="C37" s="138" t="s">
         <v>635</v>
       </c>
-      <c r="D33" s="147" t="s">
+      <c r="D37" s="139" t="s">
         <v>636</v>
       </c>
-      <c r="E33" s="148" t="s">
+      <c r="E37" s="140" t="s">
         <v>641</v>
       </c>
-      <c r="F33" s="147" t="s">
+      <c r="F37" s="139" t="s">
         <v>640</v>
       </c>
-      <c r="G33" s="146">
+      <c r="G37" s="138">
         <v>2</v>
       </c>
-      <c r="H33" s="146">
+      <c r="H37" s="138">
         <v>1.5</v>
       </c>
-      <c r="I33" s="146">
+      <c r="I37" s="138">
         <v>3.5</v>
       </c>
-      <c r="J33" s="146" t="s">
+      <c r="J37" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K33" s="146">
+      <c r="K37" s="138">
         <v>53.5</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A34" s="154" t="s">
+    <row r="38" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A38" s="146" t="s">
         <v>110</v>
       </c>
-      <c r="B34" s="146" t="s">
+      <c r="B38" s="138" t="s">
         <v>642</v>
       </c>
-      <c r="C34" s="146" t="s">
+      <c r="C38" s="138" t="s">
         <v>643</v>
       </c>
-      <c r="D34" s="147" t="s">
+      <c r="D38" s="139" t="s">
         <v>644</v>
       </c>
-      <c r="E34" s="148" t="s">
+      <c r="E38" s="140" t="s">
         <v>645</v>
       </c>
-      <c r="F34" s="147" t="s">
+      <c r="F38" s="139" t="s">
         <v>646</v>
       </c>
-      <c r="G34" s="146">
+      <c r="G38" s="138">
         <v>2</v>
       </c>
-      <c r="H34" s="146">
+      <c r="H38" s="138">
         <v>0.5</v>
       </c>
-      <c r="I34" s="146">
+      <c r="I38" s="138">
         <v>2.5</v>
       </c>
-      <c r="J34" s="146" t="s">
+      <c r="J38" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K34" s="146">
+      <c r="K38" s="138">
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A35" s="154" t="s">
+    <row r="39" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A39" s="146" t="s">
         <v>110</v>
       </c>
-      <c r="B35" s="146" t="s">
+      <c r="B39" s="138" t="s">
         <v>642</v>
       </c>
-      <c r="C35" s="146" t="s">
+      <c r="C39" s="138" t="s">
         <v>643</v>
       </c>
-      <c r="D35" s="147" t="s">
+      <c r="D39" s="139" t="s">
         <v>629</v>
       </c>
-      <c r="E35" s="148" t="s">
+      <c r="E39" s="140" t="s">
         <v>647</v>
       </c>
-      <c r="F35" s="147" t="s">
+      <c r="F39" s="139" t="s">
         <v>646</v>
       </c>
-      <c r="G35" s="146">
+      <c r="G39" s="138">
         <v>2</v>
       </c>
-      <c r="H35" s="146">
-        <v>1</v>
-      </c>
-      <c r="I35" s="146">
+      <c r="H39" s="138">
+        <v>1</v>
+      </c>
+      <c r="I39" s="138">
         <v>3</v>
       </c>
-      <c r="J35" s="146" t="s">
+      <c r="J39" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K35" s="146">
+      <c r="K39" s="138">
         <v>59</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A36" s="154" t="s">
+    <row r="40" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A40" s="146" t="s">
         <v>110</v>
       </c>
-      <c r="B36" s="146" t="s">
+      <c r="B40" s="138" t="s">
         <v>642</v>
       </c>
-      <c r="C36" s="146" t="s">
+      <c r="C40" s="138" t="s">
         <v>643</v>
       </c>
-      <c r="D36" s="147" t="s">
+      <c r="D40" s="139" t="s">
         <v>592</v>
       </c>
-      <c r="E36" s="148" t="s">
+      <c r="E40" s="140" t="s">
         <v>648</v>
       </c>
-      <c r="F36" s="147" t="s">
+      <c r="F40" s="139" t="s">
         <v>646</v>
       </c>
-      <c r="G36" s="146">
+      <c r="G40" s="138">
         <v>1.5</v>
       </c>
-      <c r="H36" s="146">
+      <c r="H40" s="138">
         <v>0.5</v>
       </c>
-      <c r="I36" s="146">
+      <c r="I40" s="138">
         <v>2</v>
       </c>
-      <c r="J36" s="146" t="s">
+      <c r="J40" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K36" s="146">
+      <c r="K40" s="138">
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A37" s="154" t="s">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41" s="156"/>
+      <c r="B41" s="157"/>
+      <c r="C41" s="157"/>
+      <c r="D41" s="157"/>
+      <c r="E41" s="157"/>
+      <c r="F41" s="157"/>
+      <c r="G41" s="157"/>
+      <c r="H41" s="157"/>
+      <c r="I41" s="157"/>
+      <c r="J41" s="157"/>
+      <c r="K41" s="158"/>
+    </row>
+    <row r="42" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A42" s="146" t="s">
         <v>182</v>
       </c>
-      <c r="B37" s="146" t="s">
+      <c r="B42" s="138" t="s">
         <v>649</v>
       </c>
-      <c r="C37" s="146" t="s">
+      <c r="C42" s="138" t="s">
         <v>650</v>
       </c>
-      <c r="D37" s="147" t="s">
+      <c r="D42" s="139" t="s">
         <v>608</v>
       </c>
-      <c r="E37" s="148" t="s">
+      <c r="E42" s="140" t="s">
         <v>337</v>
       </c>
-      <c r="F37" s="147" t="s">
+      <c r="F42" s="139" t="s">
         <v>646</v>
       </c>
-      <c r="G37" s="146">
+      <c r="G42" s="138">
         <v>2</v>
       </c>
-      <c r="H37" s="146">
-        <v>1</v>
-      </c>
-      <c r="I37" s="146">
+      <c r="H42" s="138">
+        <v>1</v>
+      </c>
+      <c r="I42" s="138">
         <v>3</v>
       </c>
-      <c r="J37" s="146" t="s">
+      <c r="J42" s="138" t="s">
         <v>116</v>
       </c>
-      <c r="K37" s="146">
+      <c r="K42" s="138">
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" s="154" t="s">
+    <row r="43" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A43" s="146" t="s">
         <v>182</v>
       </c>
-      <c r="B38" s="146" t="s">
+      <c r="B43" s="138" t="s">
         <v>649</v>
       </c>
-      <c r="C38" s="146" t="s">
+      <c r="C43" s="138" t="s">
         <v>650</v>
       </c>
-      <c r="D38" s="147" t="s">
+      <c r="D43" s="139" t="s">
         <v>608</v>
       </c>
-      <c r="E38" s="148" t="s">
+      <c r="E43" s="140" t="s">
         <v>335</v>
       </c>
-      <c r="F38" s="147" t="s">
+      <c r="F43" s="139" t="s">
         <v>646</v>
       </c>
-      <c r="G38" s="146">
+      <c r="G43" s="138">
         <v>1.5</v>
       </c>
-      <c r="H38" s="146">
+      <c r="H43" s="138">
         <v>0.5</v>
       </c>
-      <c r="I38" s="146">
+      <c r="I43" s="138">
         <v>2</v>
       </c>
-      <c r="J38" s="146" t="s">
+      <c r="J43" s="138" t="s">
         <v>116</v>
       </c>
-      <c r="K38" s="146">
+      <c r="K43" s="138">
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="154" t="s">
+    <row r="44" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A44" s="146" t="s">
         <v>182</v>
       </c>
-      <c r="B39" s="146" t="s">
+      <c r="B44" s="138" t="s">
         <v>649</v>
       </c>
-      <c r="C39" s="146" t="s">
+      <c r="C44" s="138" t="s">
         <v>650</v>
       </c>
-      <c r="D39" s="147" t="s">
+      <c r="D44" s="139" t="s">
         <v>651</v>
       </c>
-      <c r="E39" s="148" t="s">
+      <c r="E44" s="140" t="s">
         <v>652</v>
       </c>
-      <c r="F39" s="147" t="s">
+      <c r="F44" s="139" t="s">
         <v>646</v>
       </c>
-      <c r="G39" s="146">
+      <c r="G44" s="138">
         <v>1.5</v>
       </c>
-      <c r="H39" s="146">
+      <c r="H44" s="138">
         <v>0.5</v>
       </c>
-      <c r="I39" s="146">
+      <c r="I44" s="138">
         <v>2</v>
       </c>
-      <c r="J39" s="146" t="s">
+      <c r="J44" s="138" t="s">
         <v>116</v>
       </c>
-      <c r="K39" s="146">
+      <c r="K44" s="138">
         <v>68</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="154" t="s">
+    <row r="45" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A45" s="146" t="s">
         <v>182</v>
       </c>
-      <c r="B40" s="146" t="s">
+      <c r="B45" s="138" t="s">
         <v>649</v>
       </c>
-      <c r="C40" s="146" t="s">
+      <c r="C45" s="138" t="s">
         <v>650</v>
       </c>
-      <c r="D40" s="147" t="s">
+      <c r="D45" s="139" t="s">
         <v>653</v>
       </c>
-      <c r="E40" s="148" t="s">
+      <c r="E45" s="140" t="s">
         <v>654</v>
       </c>
-      <c r="F40" s="147" t="s">
+      <c r="F45" s="139" t="s">
         <v>646</v>
       </c>
-      <c r="G40" s="146">
+      <c r="G45" s="138">
         <v>2</v>
       </c>
-      <c r="H40" s="146">
-        <v>1</v>
-      </c>
-      <c r="I40" s="146">
+      <c r="H45" s="138">
+        <v>1</v>
+      </c>
+      <c r="I45" s="138">
         <v>3</v>
       </c>
-      <c r="J40" s="146" t="s">
+      <c r="J45" s="138" t="s">
         <v>257</v>
       </c>
-      <c r="K40" s="146">
+      <c r="K45" s="138">
         <v>71</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A41" s="155" t="s">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A46" s="156"/>
+      <c r="B46" s="157"/>
+      <c r="C46" s="157"/>
+      <c r="D46" s="157"/>
+      <c r="E46" s="157"/>
+      <c r="F46" s="157"/>
+      <c r="G46" s="157"/>
+      <c r="H46" s="157"/>
+      <c r="I46" s="157"/>
+      <c r="J46" s="157"/>
+      <c r="K46" s="158"/>
+    </row>
+    <row r="47" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A47" s="147" t="s">
         <v>162</v>
       </c>
-      <c r="B41" s="146" t="s">
+      <c r="B47" s="138" t="s">
         <v>655</v>
       </c>
-      <c r="C41" s="146" t="s">
+      <c r="C47" s="138" t="s">
         <v>656</v>
       </c>
-      <c r="D41" s="147" t="s">
+      <c r="D47" s="139" t="s">
         <v>657</v>
       </c>
-      <c r="E41" s="148" t="s">
+      <c r="E47" s="140" t="s">
         <v>658</v>
       </c>
-      <c r="F41" s="147" t="s">
+      <c r="F47" s="139" t="s">
         <v>659</v>
       </c>
-      <c r="G41" s="146">
+      <c r="G47" s="138">
         <v>3.5</v>
       </c>
-      <c r="H41" s="146">
-        <v>1</v>
-      </c>
-      <c r="I41" s="146">
+      <c r="H47" s="138">
+        <v>1</v>
+      </c>
+      <c r="I47" s="138">
         <v>4.5</v>
       </c>
-      <c r="J41" s="146" t="s">
+      <c r="J47" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K41" s="146">
+      <c r="K47" s="138">
         <v>75.5</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A42" s="155" t="s">
+    <row r="48" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A48" s="147" t="s">
         <v>162</v>
       </c>
-      <c r="B42" s="146" t="s">
+      <c r="B48" s="138" t="s">
         <v>655</v>
       </c>
-      <c r="C42" s="146" t="s">
+      <c r="C48" s="138" t="s">
         <v>656</v>
       </c>
-      <c r="D42" s="147" t="s">
+      <c r="D48" s="139" t="s">
         <v>651</v>
       </c>
-      <c r="E42" s="148" t="s">
+      <c r="E48" s="140" t="s">
         <v>660</v>
       </c>
-      <c r="F42" s="147" t="s">
+      <c r="F48" s="139" t="s">
         <v>659</v>
       </c>
-      <c r="G42" s="146">
+      <c r="G48" s="138">
         <v>2.5</v>
       </c>
-      <c r="H42" s="146">
-        <v>1</v>
-      </c>
-      <c r="I42" s="146">
+      <c r="H48" s="138">
+        <v>1</v>
+      </c>
+      <c r="I48" s="138">
         <v>3.5</v>
       </c>
-      <c r="J42" s="146" t="s">
+      <c r="J48" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K42" s="146">
+      <c r="K48" s="138">
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A43" s="155" t="s">
+    <row r="49" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A49" s="147" t="s">
         <v>162</v>
       </c>
-      <c r="B43" s="146" t="s">
+      <c r="B49" s="138" t="s">
         <v>655</v>
       </c>
-      <c r="C43" s="146" t="s">
+      <c r="C49" s="138" t="s">
         <v>656</v>
       </c>
-      <c r="D43" s="147" t="s">
+      <c r="D49" s="139" t="s">
         <v>661</v>
       </c>
-      <c r="E43" s="148" t="s">
+      <c r="E49" s="140" t="s">
         <v>662</v>
       </c>
-      <c r="F43" s="147" t="s">
+      <c r="F49" s="139" t="s">
         <v>659</v>
       </c>
-      <c r="G43" s="146">
-        <v>1</v>
-      </c>
-      <c r="H43" s="146">
+      <c r="G49" s="138">
+        <v>1</v>
+      </c>
+      <c r="H49" s="138">
         <v>0.5</v>
       </c>
-      <c r="I43" s="146">
+      <c r="I49" s="138">
         <v>1.5</v>
       </c>
-      <c r="J43" s="146" t="s">
+      <c r="J49" s="138" t="s">
         <v>116</v>
       </c>
-      <c r="K43" s="146">
+      <c r="K49" s="138">
         <v>80.5</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="155" t="s">
+    <row r="50" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A50" s="147" t="s">
         <v>333</v>
       </c>
-      <c r="B44" s="146" t="s">
+      <c r="B50" s="138" t="s">
         <v>663</v>
       </c>
-      <c r="C44" s="146" t="s">
+      <c r="C50" s="138" t="s">
         <v>664</v>
       </c>
-      <c r="D44" s="147" t="s">
+      <c r="D50" s="139" t="s">
         <v>636</v>
       </c>
-      <c r="E44" s="148" t="s">
+      <c r="E50" s="140" t="s">
         <v>665</v>
       </c>
-      <c r="F44" s="147" t="s">
+      <c r="F50" s="139" t="s">
         <v>666</v>
       </c>
-      <c r="G44" s="146">
+      <c r="G50" s="138">
         <v>3</v>
       </c>
-      <c r="H44" s="146">
-        <v>1</v>
-      </c>
-      <c r="I44" s="146">
+      <c r="H50" s="138">
+        <v>1</v>
+      </c>
+      <c r="I50" s="138">
         <v>4</v>
       </c>
-      <c r="J44" s="146" t="s">
+      <c r="J50" s="138" t="s">
         <v>257</v>
       </c>
-      <c r="K44" s="146">
+      <c r="K50" s="138">
         <v>84.5</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A45" s="155" t="s">
+    <row r="51" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A51" s="147" t="s">
         <v>333</v>
       </c>
-      <c r="B45" s="146" t="s">
+      <c r="B51" s="138" t="s">
         <v>663</v>
       </c>
-      <c r="C45" s="146" t="s">
+      <c r="C51" s="138" t="s">
         <v>664</v>
       </c>
-      <c r="D45" s="147" t="s">
+      <c r="D51" s="139" t="s">
         <v>625</v>
       </c>
-      <c r="E45" s="148" t="s">
+      <c r="E51" s="140" t="s">
         <v>667</v>
       </c>
-      <c r="F45" s="147" t="s">
+      <c r="F51" s="139" t="s">
         <v>594</v>
       </c>
-      <c r="G45" s="146">
+      <c r="G51" s="138">
         <v>3</v>
       </c>
-      <c r="H45" s="146">
+      <c r="H51" s="138">
         <v>1.5</v>
       </c>
-      <c r="I45" s="146">
+      <c r="I51" s="138">
         <v>4.5</v>
       </c>
-      <c r="J45" s="146" t="s">
+      <c r="J51" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K45" s="146">
+      <c r="K51" s="138">
         <v>89</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A46" s="155" t="s">
+    <row r="52" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A52" s="147" t="s">
         <v>333</v>
       </c>
-      <c r="B46" s="146" t="s">
+      <c r="B52" s="138" t="s">
         <v>663</v>
       </c>
-      <c r="C46" s="146" t="s">
+      <c r="C52" s="138" t="s">
         <v>664</v>
       </c>
-      <c r="D46" s="147" t="s">
+      <c r="D52" s="139" t="s">
         <v>608</v>
       </c>
-      <c r="E46" s="148" t="s">
+      <c r="E52" s="140" t="s">
         <v>668</v>
       </c>
-      <c r="F46" s="147" t="s">
+      <c r="F52" s="139" t="s">
         <v>669</v>
       </c>
-      <c r="G46" s="146">
+      <c r="G52" s="138">
         <v>2</v>
       </c>
-      <c r="H46" s="146">
-        <v>1</v>
-      </c>
-      <c r="I46" s="146">
+      <c r="H52" s="138">
+        <v>1</v>
+      </c>
+      <c r="I52" s="138">
         <v>3</v>
       </c>
-      <c r="J46" s="146" t="s">
+      <c r="J52" s="138" t="s">
         <v>116</v>
       </c>
-      <c r="K46" s="146">
+      <c r="K52" s="138">
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A47" s="156" t="s">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A53" s="156"/>
+      <c r="B53" s="157"/>
+      <c r="C53" s="157"/>
+      <c r="D53" s="157"/>
+      <c r="E53" s="157"/>
+      <c r="F53" s="157"/>
+      <c r="G53" s="157"/>
+      <c r="H53" s="157"/>
+      <c r="I53" s="157"/>
+      <c r="J53" s="157"/>
+      <c r="K53" s="158"/>
+    </row>
+    <row r="54" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A54" s="148" t="s">
         <v>135</v>
       </c>
-      <c r="B47" s="146" t="s">
+      <c r="B54" s="138" t="s">
         <v>670</v>
       </c>
-      <c r="C47" s="146" t="s">
+      <c r="C54" s="138" t="s">
         <v>671</v>
       </c>
-      <c r="D47" s="147" t="s">
+      <c r="D54" s="139" t="s">
         <v>672</v>
       </c>
-      <c r="E47" s="148" t="s">
+      <c r="E54" s="140" t="s">
         <v>673</v>
       </c>
-      <c r="F47" s="147" t="s">
+      <c r="F54" s="139" t="s">
         <v>594</v>
       </c>
-      <c r="G47" s="146">
+      <c r="G54" s="138">
         <v>2</v>
       </c>
-      <c r="H47" s="146">
-        <v>1</v>
-      </c>
-      <c r="I47" s="146">
+      <c r="H54" s="138">
+        <v>1</v>
+      </c>
+      <c r="I54" s="138">
         <v>3</v>
       </c>
-      <c r="J47" s="146" t="s">
+      <c r="J54" s="138" t="s">
         <v>116</v>
       </c>
-      <c r="K47" s="146">
+      <c r="K54" s="138">
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="156" t="s">
+    <row r="55" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A55" s="148" t="s">
         <v>135</v>
       </c>
-      <c r="B48" s="146" t="s">
+      <c r="B55" s="138" t="s">
         <v>670</v>
       </c>
-      <c r="C48" s="146" t="s">
+      <c r="C55" s="138" t="s">
         <v>671</v>
       </c>
-      <c r="D48" s="147" t="s">
+      <c r="D55" s="139" t="s">
         <v>674</v>
       </c>
-      <c r="E48" s="148" t="s">
+      <c r="E55" s="140" t="s">
         <v>675</v>
       </c>
-      <c r="F48" s="147" t="s">
+      <c r="F55" s="139" t="s">
         <v>594</v>
       </c>
-      <c r="G48" s="146">
+      <c r="G55" s="138">
         <v>2</v>
       </c>
-      <c r="H48" s="146">
-        <v>1</v>
-      </c>
-      <c r="I48" s="146">
+      <c r="H55" s="138">
+        <v>1</v>
+      </c>
+      <c r="I55" s="138">
         <v>3</v>
       </c>
-      <c r="J48" s="146" t="s">
+      <c r="J55" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K48" s="146">
+      <c r="K55" s="138">
         <v>98</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A49" s="156" t="s">
+    <row r="56" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A56" s="148" t="s">
         <v>135</v>
       </c>
-      <c r="B49" s="146" t="s">
+      <c r="B56" s="138" t="s">
         <v>670</v>
       </c>
-      <c r="C49" s="146" t="s">
+      <c r="C56" s="138" t="s">
         <v>671</v>
       </c>
-      <c r="D49" s="147" t="s">
+      <c r="D56" s="139" t="s">
         <v>676</v>
       </c>
-      <c r="E49" s="148" t="s">
+      <c r="E56" s="140" t="s">
         <v>677</v>
       </c>
-      <c r="F49" s="147" t="s">
+      <c r="F56" s="139" t="s">
         <v>594</v>
       </c>
-      <c r="G49" s="146">
-        <v>1</v>
-      </c>
-      <c r="H49" s="146">
+      <c r="G56" s="138">
+        <v>1</v>
+      </c>
+      <c r="H56" s="138">
         <v>4</v>
       </c>
-      <c r="I49" s="146">
+      <c r="I56" s="138">
         <v>5</v>
       </c>
-      <c r="J49" s="146" t="s">
+      <c r="J56" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="K49" s="146">
+      <c r="K56" s="138">
         <v>103</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A50" s="157"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A51" s="149" t="s">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A57" s="149"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A58" s="141" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A52" s="158" t="s">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A59" s="150" t="s">
         <v>88</v>
       </c>
-      <c r="B52" s="143" t="s">
+      <c r="B59" t="s">
         <v>679</v>
       </c>
-      <c r="D52" s="143" t="s">
+      <c r="D59" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A53" s="158" t="s">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A60" s="150" t="s">
         <v>119</v>
       </c>
-      <c r="B53" s="143" t="s">
+      <c r="B60" t="s">
         <v>681</v>
       </c>
-      <c r="D53" s="143" t="s">
+      <c r="D60" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A54" s="159" t="s">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A61" s="151" t="s">
         <v>311</v>
       </c>
-      <c r="B54" s="143" t="s">
+      <c r="B61" t="s">
         <v>683</v>
       </c>
-      <c r="D54" s="143" t="s">
+      <c r="D61" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A55" s="159" t="s">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A62" s="151" t="s">
         <v>158</v>
       </c>
-      <c r="B55" s="143" t="s">
+      <c r="B62" t="s">
         <v>685</v>
       </c>
-      <c r="D55" s="143" t="s">
+      <c r="D62" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A56" s="160" t="s">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A63" s="152" t="s">
         <v>350</v>
       </c>
-      <c r="B56" s="143" t="s">
+      <c r="B63" t="s">
         <v>687</v>
       </c>
-      <c r="D56" s="143" t="s">
+      <c r="D63" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A57" s="161" t="s">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A64" s="153" t="s">
         <v>110</v>
       </c>
-      <c r="B57" s="143" t="s">
+      <c r="B64" t="s">
         <v>689</v>
       </c>
-      <c r="D57" s="143" t="s">
+      <c r="D64" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A58" s="161" t="s">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" s="153" t="s">
         <v>182</v>
       </c>
-      <c r="B58" s="143" t="s">
+      <c r="B65" t="s">
         <v>691</v>
       </c>
-      <c r="D58" s="143" t="s">
+      <c r="D65" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A59" s="162" t="s">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" s="154" t="s">
         <v>162</v>
       </c>
-      <c r="B59" s="143" t="s">
+      <c r="B66" t="s">
         <v>692</v>
       </c>
-      <c r="D59" s="143" t="s">
+      <c r="D66" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A60" s="162" t="s">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" s="154" t="s">
         <v>333</v>
       </c>
-      <c r="B60" s="143" t="s">
+      <c r="B67" t="s">
         <v>694</v>
       </c>
-      <c r="D60" s="143" t="s">
+      <c r="D67" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A61" s="163" t="s">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" s="155" t="s">
         <v>135</v>
       </c>
-      <c r="B61" s="143" t="s">
+      <c r="B68" t="s">
         <v>696</v>
       </c>
-      <c r="D61" s="143" t="s">
+      <c r="D68" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A62" s="149" t="s">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="141" t="s">
         <v>698</v>
       </c>
-      <c r="D62" s="149" t="s">
+      <c r="D69" s="141" t="s">
         <v>699</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="8">
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="A53:K53"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="A34:K34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
